--- a/research/traditional_assets/database/data/mexico/mexico_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_drugs_pharmaceutical.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1065594692142295</v>
+        <v>0.1062712908065868</v>
       </c>
       <c r="C2">
-        <v>1430.321399662002</v>
+        <v>1419.406194016835</v>
       </c>
       <c r="D2">
-        <v>1336.921399662002</v>
+        <v>1340.766194016835</v>
       </c>
       <c r="E2">
-        <v>-336.4</v>
+        <v>-321.64</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.76</v>
       </c>
       <c r="G2">
         <v>93.40000000000001</v>
@@ -1457,28 +1457,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.742428</v>
       </c>
       <c r="N2">
-        <v>219.6566666666667</v>
+        <v>218.9142386666667</v>
       </c>
       <c r="O2">
-        <v>65.89700000000001</v>
+        <v>65.67427160000001</v>
       </c>
       <c r="P2">
-        <v>153.7596666666667</v>
+        <v>153.2399670666667</v>
       </c>
       <c r="Q2">
-        <v>157.7696666666667</v>
+        <v>157.2499670666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1065594692142295</v>
+        <v>0.106989081622815</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8903756942403465</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>295.8625842056964</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1062712908065868</v>
+        <v>0.1059831123989441</v>
       </c>
       <c r="C3">
-        <v>1419.406194016835</v>
+        <v>1408.513166307388</v>
       </c>
       <c r="D3">
-        <v>1340.766194016835</v>
+        <v>1344.633166307388</v>
       </c>
       <c r="E3">
-        <v>-321.64</v>
+        <v>-306.88</v>
       </c>
       <c r="F3">
-        <v>14.76</v>
+        <v>29.52</v>
       </c>
       <c r="G3">
         <v>93.40000000000001</v>
@@ -1539,28 +1539,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M3">
-        <v>0.742428</v>
+        <v>1.484856</v>
       </c>
       <c r="N3">
-        <v>218.9142386666667</v>
+        <v>218.1718106666667</v>
       </c>
       <c r="O3">
-        <v>65.67427160000001</v>
+        <v>65.4515432</v>
       </c>
       <c r="P3">
-        <v>153.2399670666667</v>
+        <v>152.7202674666667</v>
       </c>
       <c r="Q3">
-        <v>157.2499670666667</v>
+        <v>156.7302674666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.106989081622815</v>
+        <v>0.1074274616315756</v>
       </c>
       <c r="T3">
-        <v>0.8903756942403465</v>
+        <v>0.8967546575176093</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>295.8625842056964</v>
+        <v>147.9312921028481</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1059831123989441</v>
+        <v>0.1056949339913014</v>
       </c>
       <c r="C4">
-        <v>1408.513166307388</v>
+        <v>1397.642508982265</v>
       </c>
       <c r="D4">
-        <v>1344.633166307388</v>
+        <v>1348.522508982265</v>
       </c>
       <c r="E4">
-        <v>-306.88</v>
+        <v>-292.12</v>
       </c>
       <c r="F4">
-        <v>29.52</v>
+        <v>44.28</v>
       </c>
       <c r="G4">
         <v>93.40000000000001</v>
@@ -1621,28 +1621,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M4">
-        <v>1.484856</v>
+        <v>2.227284</v>
       </c>
       <c r="N4">
-        <v>218.1718106666667</v>
+        <v>217.4293826666667</v>
       </c>
       <c r="O4">
-        <v>65.4515432</v>
+        <v>65.22881480000001</v>
       </c>
       <c r="P4">
-        <v>152.7202674666667</v>
+        <v>152.2005678666667</v>
       </c>
       <c r="Q4">
-        <v>156.7302674666667</v>
+        <v>156.2105678666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1074274616315756</v>
+        <v>0.1078748804034035</v>
       </c>
       <c r="T4">
-        <v>0.8967546575176093</v>
+        <v>0.9032651458108981</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>147.9312921028481</v>
+        <v>98.62086140189876</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1056949339913014</v>
+        <v>0.1054067555836587</v>
       </c>
       <c r="C5">
-        <v>1397.642508982265</v>
+        <v>1386.794416723153</v>
       </c>
       <c r="D5">
-        <v>1348.522508982265</v>
+        <v>1352.434416723153</v>
       </c>
       <c r="E5">
-        <v>-292.12</v>
+        <v>-277.36</v>
       </c>
       <c r="F5">
-        <v>44.28</v>
+        <v>59.04</v>
       </c>
       <c r="G5">
         <v>93.40000000000001</v>
@@ -1703,28 +1703,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M5">
-        <v>2.227284</v>
+        <v>2.969712</v>
       </c>
       <c r="N5">
-        <v>217.4293826666667</v>
+        <v>216.6869546666667</v>
       </c>
       <c r="O5">
-        <v>65.22881480000001</v>
+        <v>65.00608640000002</v>
       </c>
       <c r="P5">
-        <v>152.2005678666667</v>
+        <v>151.6808682666667</v>
       </c>
       <c r="Q5">
-        <v>156.2105678666667</v>
+        <v>155.6908682666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1078748804034035</v>
+        <v>0.1083316203996445</v>
       </c>
       <c r="T5">
-        <v>0.9032651458108981</v>
+        <v>0.9099112692769639</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>98.62086140189876</v>
+        <v>73.96564605142409</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1054067555836587</v>
+        <v>0.105118577176016</v>
       </c>
       <c r="C6">
-        <v>1386.794416723153</v>
+        <v>1375.96908647731</v>
       </c>
       <c r="D6">
-        <v>1352.434416723153</v>
+        <v>1356.36908647731</v>
       </c>
       <c r="E6">
-        <v>-277.36</v>
+        <v>-262.6</v>
       </c>
       <c r="F6">
-        <v>59.04</v>
+        <v>73.8</v>
       </c>
       <c r="G6">
         <v>93.40000000000001</v>
@@ -1785,28 +1785,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M6">
-        <v>2.969712</v>
+        <v>3.71214</v>
       </c>
       <c r="N6">
-        <v>216.6869546666667</v>
+        <v>215.9445266666667</v>
       </c>
       <c r="O6">
-        <v>65.00608640000002</v>
+        <v>64.78335800000001</v>
       </c>
       <c r="P6">
-        <v>151.6808682666667</v>
+        <v>151.1611686666667</v>
       </c>
       <c r="Q6">
-        <v>155.6908682666667</v>
+        <v>155.1711686666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1083316203996445</v>
+        <v>0.1087979759747537</v>
       </c>
       <c r="T6">
-        <v>0.9099112692769639</v>
+        <v>0.9166973111317889</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.96564605142409</v>
+        <v>59.17251684113926</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.105118577176016</v>
+        <v>0.1048303987683733</v>
       </c>
       <c r="C7">
-        <v>1375.96908647731</v>
+        <v>1365.166717490613</v>
       </c>
       <c r="D7">
-        <v>1356.36908647731</v>
+        <v>1360.326717490613</v>
       </c>
       <c r="E7">
-        <v>-262.6</v>
+        <v>-247.84</v>
       </c>
       <c r="F7">
-        <v>73.8</v>
+        <v>88.56</v>
       </c>
       <c r="G7">
         <v>93.40000000000001</v>
@@ -1867,28 +1867,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M7">
-        <v>3.71214</v>
+        <v>4.454568</v>
       </c>
       <c r="N7">
-        <v>215.9445266666667</v>
+        <v>215.2020986666667</v>
       </c>
       <c r="O7">
-        <v>64.78335800000001</v>
+        <v>64.56062960000001</v>
       </c>
       <c r="P7">
-        <v>151.1611686666667</v>
+        <v>150.6414690666667</v>
       </c>
       <c r="Q7">
-        <v>155.1711686666667</v>
+        <v>154.6514690666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1087979759747537</v>
+        <v>0.1092742540089078</v>
       </c>
       <c r="T7">
-        <v>0.9166973111317889</v>
+        <v>0.9236277368558654</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>59.17251684113926</v>
+        <v>49.31043070094938</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1048303987683733</v>
+        <v>0.1045422203607307</v>
       </c>
       <c r="C8">
-        <v>1365.166717490613</v>
+        <v>1354.387511341193</v>
       </c>
       <c r="D8">
-        <v>1360.326717490613</v>
+        <v>1364.307511341193</v>
       </c>
       <c r="E8">
-        <v>-247.84</v>
+        <v>-233.08</v>
       </c>
       <c r="F8">
-        <v>88.56</v>
+        <v>103.32</v>
       </c>
       <c r="G8">
         <v>93.40000000000001</v>
@@ -1949,28 +1949,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M8">
-        <v>4.454568</v>
+        <v>5.196996</v>
       </c>
       <c r="N8">
-        <v>215.2020986666667</v>
+        <v>214.4596706666667</v>
       </c>
       <c r="O8">
-        <v>64.56062960000001</v>
+        <v>64.3379012</v>
       </c>
       <c r="P8">
-        <v>150.6414690666667</v>
+        <v>150.1217694666667</v>
       </c>
       <c r="Q8">
-        <v>154.6514690666667</v>
+        <v>154.1317694666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1092742540089078</v>
+        <v>0.1097607745814308</v>
       </c>
       <c r="T8">
-        <v>0.9236277368558654</v>
+        <v>0.9307072039933632</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.31043070094938</v>
+        <v>42.26608345795662</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1045422203607307</v>
+        <v>0.104254041953088</v>
       </c>
       <c r="C9">
-        <v>1354.387511341193</v>
+        <v>1343.631671973661</v>
       </c>
       <c r="D9">
-        <v>1364.307511341193</v>
+        <v>1368.311671973661</v>
       </c>
       <c r="E9">
-        <v>-233.08</v>
+        <v>-218.32</v>
       </c>
       <c r="F9">
-        <v>103.32</v>
+        <v>118.08</v>
       </c>
       <c r="G9">
         <v>93.40000000000001</v>
@@ -2031,28 +2031,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M9">
-        <v>5.196996</v>
+        <v>5.939424</v>
       </c>
       <c r="N9">
-        <v>214.4596706666667</v>
+        <v>213.7172426666667</v>
       </c>
       <c r="O9">
-        <v>64.3379012</v>
+        <v>64.11517280000001</v>
       </c>
       <c r="P9">
-        <v>150.1217694666667</v>
+        <v>149.6020698666667</v>
       </c>
       <c r="Q9">
-        <v>154.1317694666667</v>
+        <v>153.6120698666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1097607745814308</v>
+        <v>0.1102578716881391</v>
       </c>
       <c r="T9">
-        <v>0.9307072039933632</v>
+        <v>0.9379405725903717</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.26608345795661</v>
+        <v>36.98282302571204</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.104254041953088</v>
+        <v>0.1039658635454453</v>
       </c>
       <c r="C10">
-        <v>1343.631671973661</v>
+        <v>1332.899405733935</v>
       </c>
       <c r="D10">
-        <v>1368.311671973661</v>
+        <v>1372.339405733934</v>
       </c>
       <c r="E10">
-        <v>-218.32</v>
+        <v>-203.56</v>
       </c>
       <c r="F10">
-        <v>118.08</v>
+        <v>132.84</v>
       </c>
       <c r="G10">
         <v>93.40000000000001</v>
@@ -2113,28 +2113,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M10">
-        <v>5.939424</v>
+        <v>6.681852</v>
       </c>
       <c r="N10">
-        <v>213.7172426666667</v>
+        <v>212.9748146666667</v>
       </c>
       <c r="O10">
-        <v>64.11517280000001</v>
+        <v>63.89244440000001</v>
       </c>
       <c r="P10">
-        <v>149.6020698666667</v>
+        <v>149.0823702666667</v>
       </c>
       <c r="Q10">
-        <v>153.6120698666667</v>
+        <v>153.0923702666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1102578716881391</v>
+        <v>0.1107658940059838</v>
       </c>
       <c r="T10">
-        <v>0.9379405725903717</v>
+        <v>0.9453329163213802</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.98282302571204</v>
+        <v>32.87362046729959</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1039658635454453</v>
+        <v>0.1036776851378026</v>
       </c>
       <c r="C11">
-        <v>1332.899405733935</v>
+        <v>1322.190921404688</v>
       </c>
       <c r="D11">
-        <v>1372.339405733934</v>
+        <v>1376.390921404688</v>
       </c>
       <c r="E11">
-        <v>-203.56</v>
+        <v>-188.8</v>
       </c>
       <c r="F11">
-        <v>132.84</v>
+        <v>147.6</v>
       </c>
       <c r="G11">
         <v>93.40000000000001</v>
@@ -2195,28 +2195,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M11">
-        <v>6.681852</v>
+        <v>7.42428</v>
       </c>
       <c r="N11">
-        <v>212.9748146666667</v>
+        <v>212.2323866666667</v>
       </c>
       <c r="O11">
-        <v>63.89244440000001</v>
+        <v>63.669716</v>
       </c>
       <c r="P11">
-        <v>149.0823702666667</v>
+        <v>148.5626706666667</v>
       </c>
       <c r="Q11">
-        <v>153.0923702666667</v>
+        <v>152.5726706666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1107658940059838</v>
+        <v>0.1112852057086695</v>
       </c>
       <c r="T11">
-        <v>0.9453329163213802</v>
+        <v>0.9528895343575222</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.87362046729959</v>
+        <v>29.58625842056963</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1036776851378026</v>
+        <v>0.1033895067301599</v>
       </c>
       <c r="C12">
-        <v>1322.190921404688</v>
+        <v>1311.506430241426</v>
       </c>
       <c r="D12">
-        <v>1376.390921404688</v>
+        <v>1380.466430241426</v>
       </c>
       <c r="E12">
-        <v>-188.8</v>
+        <v>-174.04</v>
       </c>
       <c r="F12">
-        <v>147.6</v>
+        <v>162.36</v>
       </c>
       <c r="G12">
         <v>93.40000000000001</v>
@@ -2277,28 +2277,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M12">
-        <v>7.42428</v>
+        <v>8.166708</v>
       </c>
       <c r="N12">
-        <v>212.2323866666667</v>
+        <v>211.4899586666667</v>
       </c>
       <c r="O12">
-        <v>63.669716</v>
+        <v>63.44698760000001</v>
       </c>
       <c r="P12">
-        <v>148.5626706666667</v>
+        <v>148.0429710666667</v>
       </c>
       <c r="Q12">
-        <v>152.5726706666667</v>
+        <v>152.0529710666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1112852057086695</v>
+        <v>0.1118161873372583</v>
       </c>
       <c r="T12">
-        <v>0.9528895343575222</v>
+        <v>0.960615964034926</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.58625842056963</v>
+        <v>26.89659856415421</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1033895067301599</v>
+        <v>0.1031013283225172</v>
       </c>
       <c r="C13">
-        <v>1311.506430241426</v>
+        <v>1300.846146009203</v>
       </c>
       <c r="D13">
-        <v>1380.466430241426</v>
+        <v>1384.566146009203</v>
       </c>
       <c r="E13">
-        <v>-174.04</v>
+        <v>-159.28</v>
       </c>
       <c r="F13">
-        <v>162.36</v>
+        <v>177.12</v>
       </c>
       <c r="G13">
         <v>93.40000000000001</v>
@@ -2359,28 +2359,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M13">
-        <v>8.166708</v>
+        <v>8.909136</v>
       </c>
       <c r="N13">
-        <v>211.4899586666667</v>
+        <v>210.7475306666667</v>
       </c>
       <c r="O13">
-        <v>63.44698760000001</v>
+        <v>63.22425920000001</v>
       </c>
       <c r="P13">
-        <v>148.0429710666667</v>
+        <v>147.5232714666667</v>
       </c>
       <c r="Q13">
-        <v>152.0529710666667</v>
+        <v>151.5332714666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1118161873372583</v>
+        <v>0.1123592367301332</v>
       </c>
       <c r="T13">
-        <v>0.960615964034926</v>
+        <v>0.9685179943868162</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.89659856415421</v>
+        <v>24.65521535047469</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1031013283225172</v>
+        <v>0.1028131499148745</v>
       </c>
       <c r="C14">
-        <v>1300.846146009203</v>
+        <v>1290.210285020001</v>
       </c>
       <c r="D14">
-        <v>1384.566146009203</v>
+        <v>1388.690285020001</v>
       </c>
       <c r="E14">
-        <v>-159.28</v>
+        <v>-144.52</v>
       </c>
       <c r="F14">
-        <v>177.12</v>
+        <v>191.88</v>
       </c>
       <c r="G14">
         <v>93.40000000000001</v>
@@ -2441,28 +2441,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M14">
-        <v>8.909136</v>
+        <v>9.651563999999999</v>
       </c>
       <c r="N14">
-        <v>210.7475306666667</v>
+        <v>210.0051026666667</v>
       </c>
       <c r="O14">
-        <v>63.22425920000001</v>
+        <v>63.0015308</v>
       </c>
       <c r="P14">
-        <v>147.5232714666667</v>
+        <v>147.0035718666667</v>
       </c>
       <c r="Q14">
-        <v>151.5332714666667</v>
+        <v>151.0135718666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1123592367301332</v>
+        <v>0.1129147700170972</v>
       </c>
       <c r="T14">
-        <v>0.9685179943868162</v>
+        <v>0.9766016806088648</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.65521535047469</v>
+        <v>22.7586603235151</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1028131499148745</v>
+        <v>0.1025249715072318</v>
       </c>
       <c r="C15">
-        <v>1290.210285020001</v>
+        <v>1279.599066170772</v>
       </c>
       <c r="D15">
-        <v>1388.690285020001</v>
+        <v>1392.839066170772</v>
       </c>
       <c r="E15">
-        <v>-144.52</v>
+        <v>-129.76</v>
       </c>
       <c r="F15">
-        <v>191.88</v>
+        <v>206.64</v>
       </c>
       <c r="G15">
         <v>93.40000000000001</v>
@@ -2523,28 +2523,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M15">
-        <v>9.651563999999999</v>
+        <v>10.393992</v>
       </c>
       <c r="N15">
-        <v>210.0051026666667</v>
+        <v>209.2626746666667</v>
       </c>
       <c r="O15">
-        <v>63.0015308</v>
+        <v>62.7788024</v>
       </c>
       <c r="P15">
-        <v>147.0035718666667</v>
+        <v>146.4838722666667</v>
       </c>
       <c r="Q15">
-        <v>151.0135718666667</v>
+        <v>150.4938722666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1129147700170972</v>
+        <v>0.1134832226828277</v>
       </c>
       <c r="T15">
-        <v>0.9766016806088648</v>
+        <v>0.9848733595337517</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.7586603235151</v>
+        <v>21.13304172897831</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1025249715072318</v>
+        <v>0.1022367930995892</v>
       </c>
       <c r="C16">
-        <v>1279.599066170772</v>
+        <v>1269.012710982168</v>
       </c>
       <c r="D16">
-        <v>1392.839066170772</v>
+        <v>1397.012710982168</v>
       </c>
       <c r="E16">
-        <v>-129.76</v>
+        <v>-114.9999999999999</v>
       </c>
       <c r="F16">
-        <v>206.64</v>
+        <v>221.4</v>
       </c>
       <c r="G16">
         <v>93.40000000000001</v>
@@ -2605,28 +2605,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M16">
-        <v>10.393992</v>
+        <v>11.13642</v>
       </c>
       <c r="N16">
-        <v>209.2626746666667</v>
+        <v>208.5202466666667</v>
       </c>
       <c r="O16">
-        <v>62.7788024</v>
+        <v>62.55607400000001</v>
       </c>
       <c r="P16">
-        <v>146.4838722666667</v>
+        <v>145.9641726666667</v>
       </c>
       <c r="Q16">
-        <v>150.4938722666667</v>
+        <v>149.9741726666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1134832226828277</v>
+        <v>0.114065050705399</v>
       </c>
       <c r="T16">
-        <v>0.9848733595337517</v>
+        <v>0.9933396661980478</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.13304172897831</v>
+        <v>19.72417228037975</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1022367930995892</v>
+        <v>0.1019486146919465</v>
       </c>
       <c r="C17">
-        <v>1269.012710982168</v>
+        <v>1258.45144363797</v>
       </c>
       <c r="D17">
-        <v>1397.012710982168</v>
+        <v>1401.21144363797</v>
       </c>
       <c r="E17">
-        <v>-115</v>
+        <v>-100.24</v>
       </c>
       <c r="F17">
-        <v>221.4</v>
+        <v>236.16</v>
       </c>
       <c r="G17">
         <v>93.40000000000001</v>
@@ -2687,28 +2687,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M17">
-        <v>11.13642</v>
+        <v>11.878848</v>
       </c>
       <c r="N17">
-        <v>208.5202466666667</v>
+        <v>207.7778186666667</v>
       </c>
       <c r="O17">
-        <v>62.55607400000001</v>
+        <v>62.3333456</v>
       </c>
       <c r="P17">
-        <v>145.9641726666667</v>
+        <v>145.4444730666667</v>
       </c>
       <c r="Q17">
-        <v>149.9741726666667</v>
+        <v>149.4544730666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.114065050705399</v>
+        <v>0.1146607317761267</v>
       </c>
       <c r="T17">
-        <v>0.9933396661980478</v>
+        <v>1.002007551592446</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.72417228037975</v>
+        <v>18.49141151285602</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1019486146919465</v>
+        <v>0.1016604362843038</v>
       </c>
       <c r="C18">
-        <v>1258.45144363797</v>
+        <v>1247.915491025229</v>
       </c>
       <c r="D18">
-        <v>1401.21144363797</v>
+        <v>1405.435491025229</v>
       </c>
       <c r="E18">
-        <v>-100.24</v>
+        <v>-85.47999999999996</v>
       </c>
       <c r="F18">
-        <v>236.16</v>
+        <v>250.92</v>
       </c>
       <c r="G18">
         <v>93.40000000000001</v>
@@ -2769,28 +2769,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M18">
-        <v>11.878848</v>
+        <v>12.621276</v>
       </c>
       <c r="N18">
-        <v>207.7778186666667</v>
+        <v>207.0353906666667</v>
       </c>
       <c r="O18">
-        <v>62.3333456</v>
+        <v>62.11061720000001</v>
       </c>
       <c r="P18">
-        <v>145.4444730666667</v>
+        <v>144.9247734666667</v>
       </c>
       <c r="Q18">
-        <v>149.4544730666667</v>
+        <v>148.9347734666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1146607317761267</v>
+        <v>0.1152707666075949</v>
       </c>
       <c r="T18">
-        <v>1.002007551592446</v>
+        <v>1.010884301695143</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.49141151285602</v>
+        <v>17.40368142386449</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1016604362843038</v>
+        <v>0.1013722578766611</v>
       </c>
       <c r="C19">
-        <v>1247.915491025229</v>
+        <v>1237.405082775132</v>
       </c>
       <c r="D19">
-        <v>1405.435491025229</v>
+        <v>1409.685082775132</v>
       </c>
       <c r="E19">
-        <v>-85.47999999999996</v>
+        <v>-70.71999999999997</v>
       </c>
       <c r="F19">
-        <v>250.92</v>
+        <v>265.68</v>
       </c>
       <c r="G19">
         <v>93.40000000000001</v>
@@ -2851,28 +2851,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M19">
-        <v>12.621276</v>
+        <v>13.363704</v>
       </c>
       <c r="N19">
-        <v>207.0353906666667</v>
+        <v>206.2929626666667</v>
       </c>
       <c r="O19">
-        <v>62.11061720000001</v>
+        <v>61.8878888</v>
       </c>
       <c r="P19">
-        <v>144.9247734666667</v>
+        <v>144.4050738666667</v>
       </c>
       <c r="Q19">
-        <v>148.9347734666667</v>
+        <v>148.4150738666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1152707666075949</v>
+        <v>0.1158956803373916</v>
       </c>
       <c r="T19">
-        <v>1.010884301695143</v>
+        <v>1.019977557897906</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.40368142386449</v>
+        <v>16.43681023364979</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1013722578766611</v>
+        <v>0.1010840794690184</v>
       </c>
       <c r="C20">
-        <v>1237.405082775132</v>
+        <v>1226.920451304619</v>
       </c>
       <c r="D20">
-        <v>1409.685082775132</v>
+        <v>1413.960451304619</v>
       </c>
       <c r="E20">
-        <v>-70.71999999999997</v>
+        <v>-55.95999999999998</v>
       </c>
       <c r="F20">
-        <v>265.68</v>
+        <v>280.44</v>
       </c>
       <c r="G20">
         <v>93.40000000000001</v>
@@ -2933,28 +2933,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M20">
-        <v>13.363704</v>
+        <v>14.106132</v>
       </c>
       <c r="N20">
-        <v>206.2929626666667</v>
+        <v>205.5505346666667</v>
       </c>
       <c r="O20">
-        <v>61.8878888</v>
+        <v>61.6651604</v>
       </c>
       <c r="P20">
-        <v>144.4050738666667</v>
+        <v>143.8853742666667</v>
       </c>
       <c r="Q20">
-        <v>148.4150738666667</v>
+        <v>147.8953742666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1158956803373916</v>
+        <v>0.1165360240358252</v>
       </c>
       <c r="T20">
-        <v>1.019977557897906</v>
+        <v>1.029295338945182</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.43681023364979</v>
+        <v>15.57171495819454</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1010840794690184</v>
+        <v>0.1007959010613757</v>
       </c>
       <c r="C21">
-        <v>1226.920451304619</v>
+        <v>1216.461831858753</v>
       </c>
       <c r="D21">
-        <v>1413.960451304619</v>
+        <v>1418.261831858753</v>
       </c>
       <c r="E21">
-        <v>-55.95999999999998</v>
+        <v>-41.19999999999999</v>
       </c>
       <c r="F21">
-        <v>280.44</v>
+        <v>295.2</v>
       </c>
       <c r="G21">
         <v>93.40000000000001</v>
@@ -3015,28 +3015,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M21">
-        <v>14.106132</v>
+        <v>14.84856</v>
       </c>
       <c r="N21">
-        <v>205.5505346666667</v>
+        <v>204.8081066666667</v>
       </c>
       <c r="O21">
-        <v>61.6651604</v>
+        <v>61.44243200000001</v>
       </c>
       <c r="P21">
-        <v>143.8853742666667</v>
+        <v>143.3656746666667</v>
       </c>
       <c r="Q21">
-        <v>147.8953742666667</v>
+        <v>147.3756746666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1165360240358252</v>
+        <v>0.1171923763267196</v>
       </c>
       <c r="T21">
-        <v>1.029295338945182</v>
+        <v>1.038846064518639</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.57171495819454</v>
+        <v>14.79312921028482</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1007959010613757</v>
+        <v>0.100507722653733</v>
       </c>
       <c r="C22">
-        <v>1216.461831858753</v>
+        <v>1206.029462553868</v>
       </c>
       <c r="D22">
-        <v>1418.261831858753</v>
+        <v>1422.589462553868</v>
       </c>
       <c r="E22">
-        <v>-41.19999999999999</v>
+        <v>-26.43999999999994</v>
       </c>
       <c r="F22">
-        <v>295.2</v>
+        <v>309.96</v>
       </c>
       <c r="G22">
         <v>93.40000000000001</v>
@@ -3097,28 +3097,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M22">
-        <v>14.84856</v>
+        <v>15.590988</v>
       </c>
       <c r="N22">
-        <v>204.8081066666667</v>
+        <v>204.0656786666667</v>
       </c>
       <c r="O22">
-        <v>61.44243200000001</v>
+        <v>61.2197036</v>
       </c>
       <c r="P22">
-        <v>143.3656746666667</v>
+        <v>142.8459750666667</v>
       </c>
       <c r="Q22">
-        <v>147.3756746666667</v>
+        <v>146.8559750666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1171923763267196</v>
+        <v>0.1178653451313076</v>
       </c>
       <c r="T22">
-        <v>1.038846064518639</v>
+        <v>1.048638580612943</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.79312921028482</v>
+        <v>14.08869448598554</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.100507722653733</v>
+        <v>0.1002195442460903</v>
       </c>
       <c r="C23">
-        <v>1206.029462553869</v>
+        <v>1195.623584421512</v>
       </c>
       <c r="D23">
-        <v>1422.589462553869</v>
+        <v>1426.943584421512</v>
       </c>
       <c r="E23">
-        <v>-26.44</v>
+        <v>-11.67999999999995</v>
       </c>
       <c r="F23">
-        <v>309.96</v>
+        <v>324.72</v>
       </c>
       <c r="G23">
         <v>93.40000000000001</v>
@@ -3179,28 +3179,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M23">
-        <v>15.590988</v>
+        <v>16.333416</v>
       </c>
       <c r="N23">
-        <v>204.0656786666667</v>
+        <v>203.3232506666667</v>
       </c>
       <c r="O23">
-        <v>61.2197036</v>
+        <v>60.99697520000001</v>
       </c>
       <c r="P23">
-        <v>142.8459750666667</v>
+        <v>142.3262754666667</v>
       </c>
       <c r="Q23">
-        <v>146.8559750666667</v>
+        <v>146.3362754666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1178653451313076</v>
+        <v>0.1185555695462697</v>
       </c>
       <c r="T23">
-        <v>1.048638580612943</v>
+        <v>1.058682186863512</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.08869448598554</v>
+        <v>13.44829928207711</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1002195442460903</v>
+        <v>0.1001728658384476</v>
       </c>
       <c r="C24">
-        <v>1195.623584421512</v>
+        <v>1181.571363551235</v>
       </c>
       <c r="D24">
-        <v>1426.943584421512</v>
+        <v>1427.651363551234</v>
       </c>
       <c r="E24">
-        <v>-11.67999999999995</v>
+        <v>3.080000000000041</v>
       </c>
       <c r="F24">
-        <v>324.72</v>
+        <v>339.48</v>
       </c>
       <c r="G24">
         <v>93.40000000000001</v>
@@ -3261,45 +3261,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M24">
-        <v>16.333416</v>
+        <v>17.585064</v>
       </c>
       <c r="N24">
-        <v>203.3232506666667</v>
+        <v>202.0716026666667</v>
       </c>
       <c r="O24">
-        <v>60.99697520000001</v>
+        <v>60.62148080000001</v>
       </c>
       <c r="P24">
-        <v>142.3262754666667</v>
+        <v>141.4501218666667</v>
       </c>
       <c r="Q24">
-        <v>146.3362754666667</v>
+        <v>145.4601218666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1185555695462697</v>
+        <v>0.1192637218681138</v>
       </c>
       <c r="T24">
-        <v>1.058682186863512</v>
+        <v>1.068986666003706</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.44829928207711</v>
+        <v>12.49109281983089</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1001728658384476</v>
+        <v>0.09989518743080497</v>
       </c>
       <c r="C25">
-        <v>1181.571363551235</v>
+        <v>1171.036322901664</v>
       </c>
       <c r="D25">
-        <v>1427.651363551234</v>
+        <v>1431.876322901664</v>
       </c>
       <c r="E25">
-        <v>3.080000000000041</v>
+        <v>17.84000000000003</v>
       </c>
       <c r="F25">
-        <v>339.48</v>
+        <v>354.24</v>
       </c>
       <c r="G25">
         <v>93.40000000000001</v>
@@ -3343,28 +3343,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M25">
-        <v>17.585064</v>
+        <v>18.349632</v>
       </c>
       <c r="N25">
-        <v>202.0716026666667</v>
+        <v>201.3070346666667</v>
       </c>
       <c r="O25">
-        <v>60.62148080000001</v>
+        <v>60.39211040000001</v>
       </c>
       <c r="P25">
-        <v>141.4501218666667</v>
+        <v>140.9149242666667</v>
       </c>
       <c r="Q25">
-        <v>145.4601218666667</v>
+        <v>144.9249242666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1192637218681138</v>
+        <v>0.119990509777375</v>
       </c>
       <c r="T25">
-        <v>1.068986666003706</v>
+        <v>1.079562315647589</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.49109281983089</v>
+        <v>11.97063061900461</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09989518743080497</v>
+        <v>0.09961750902316228</v>
       </c>
       <c r="C26">
-        <v>1171.036322901664</v>
+        <v>1160.526362974863</v>
       </c>
       <c r="D26">
-        <v>1431.876322901664</v>
+        <v>1436.126362974863</v>
       </c>
       <c r="E26">
-        <v>17.84000000000003</v>
+        <v>32.60000000000002</v>
       </c>
       <c r="F26">
-        <v>354.24</v>
+        <v>369</v>
       </c>
       <c r="G26">
         <v>93.40000000000001</v>
@@ -3425,28 +3425,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M26">
-        <v>18.349632</v>
+        <v>19.1142</v>
       </c>
       <c r="N26">
-        <v>201.3070346666667</v>
+        <v>200.5424666666667</v>
       </c>
       <c r="O26">
-        <v>60.39211040000001</v>
+        <v>60.16274</v>
       </c>
       <c r="P26">
-        <v>140.9149242666667</v>
+        <v>140.3797266666667</v>
       </c>
       <c r="Q26">
-        <v>144.9249242666667</v>
+        <v>144.3897266666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.119990509777375</v>
+        <v>0.1207366786975497</v>
       </c>
       <c r="T26">
-        <v>1.079562315647589</v>
+        <v>1.090419982615309</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.97063061900461</v>
+        <v>11.49180539424442</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09961750902316228</v>
+        <v>0.09933983061551957</v>
       </c>
       <c r="C27">
-        <v>1160.526362974863</v>
+        <v>1150.041707766588</v>
       </c>
       <c r="D27">
-        <v>1436.126362974863</v>
+        <v>1440.401707766588</v>
       </c>
       <c r="E27">
-        <v>32.60000000000002</v>
+        <v>47.36000000000001</v>
       </c>
       <c r="F27">
-        <v>369</v>
+        <v>383.76</v>
       </c>
       <c r="G27">
         <v>93.40000000000001</v>
@@ -3507,28 +3507,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M27">
-        <v>19.1142</v>
+        <v>19.878768</v>
       </c>
       <c r="N27">
-        <v>200.5424666666667</v>
+        <v>199.7778986666667</v>
       </c>
       <c r="O27">
-        <v>60.16274</v>
+        <v>59.93336960000001</v>
       </c>
       <c r="P27">
-        <v>140.3797266666667</v>
+        <v>139.8445290666667</v>
       </c>
       <c r="Q27">
-        <v>144.3897266666667</v>
+        <v>143.8545290666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1207366786975497</v>
+        <v>0.1215030143452967</v>
       </c>
       <c r="T27">
-        <v>1.090419982615309</v>
+        <v>1.101571100041616</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.49180539424442</v>
+        <v>11.04981287908117</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09933983061551957</v>
+        <v>0.09906215220787691</v>
       </c>
       <c r="C28">
-        <v>1150.041707766588</v>
+        <v>1139.5825839479</v>
       </c>
       <c r="D28">
-        <v>1440.401707766588</v>
+        <v>1444.7025839479</v>
       </c>
       <c r="E28">
-        <v>47.36000000000001</v>
+        <v>62.12000000000006</v>
       </c>
       <c r="F28">
-        <v>383.76</v>
+        <v>398.52</v>
       </c>
       <c r="G28">
         <v>93.40000000000001</v>
@@ -3589,28 +3589,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M28">
-        <v>19.878768</v>
+        <v>20.643336</v>
       </c>
       <c r="N28">
-        <v>199.7778986666667</v>
+        <v>199.0133306666667</v>
       </c>
       <c r="O28">
-        <v>59.93336960000001</v>
+        <v>59.70399920000001</v>
       </c>
       <c r="P28">
-        <v>139.8445290666667</v>
+        <v>139.3093314666667</v>
       </c>
       <c r="Q28">
-        <v>143.8545290666667</v>
+        <v>143.3193314666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1215030143452967</v>
+        <v>0.1222903454902423</v>
       </c>
       <c r="T28">
-        <v>1.101571100041616</v>
+        <v>1.113027727534397</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.04981287908117</v>
+        <v>10.64056055022631</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09906215220787691</v>
+        <v>0.0987844738002342</v>
       </c>
       <c r="C29">
-        <v>1139.5825839479</v>
+        <v>1129.149220905226</v>
       </c>
       <c r="D29">
-        <v>1444.7025839479</v>
+        <v>1449.029220905226</v>
       </c>
       <c r="E29">
-        <v>62.12000000000006</v>
+        <v>76.88000000000005</v>
       </c>
       <c r="F29">
-        <v>398.52</v>
+        <v>413.28</v>
       </c>
       <c r="G29">
         <v>93.40000000000001</v>
@@ -3671,28 +3671,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M29">
-        <v>20.643336</v>
+        <v>21.407904</v>
       </c>
       <c r="N29">
-        <v>199.0133306666667</v>
+        <v>198.2487626666667</v>
       </c>
       <c r="O29">
-        <v>59.70399920000001</v>
+        <v>59.4746288</v>
       </c>
       <c r="P29">
-        <v>139.3093314666667</v>
+        <v>138.7741338666667</v>
       </c>
       <c r="Q29">
-        <v>143.3193314666667</v>
+        <v>142.7841338666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1222903454902423</v>
+        <v>0.1230995469447697</v>
       </c>
       <c r="T29">
-        <v>1.113027727534397</v>
+        <v>1.124802594679756</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.64056055022631</v>
+        <v>10.26054053057537</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0987844738002342</v>
+        <v>0.09850679539259151</v>
       </c>
       <c r="C30">
-        <v>1129.149220905226</v>
+        <v>1118.741850781135</v>
       </c>
       <c r="D30">
-        <v>1449.029220905226</v>
+        <v>1453.381850781135</v>
       </c>
       <c r="E30">
-        <v>76.88000000000005</v>
+        <v>91.6400000000001</v>
       </c>
       <c r="F30">
-        <v>413.28</v>
+        <v>428.0400000000001</v>
       </c>
       <c r="G30">
         <v>93.40000000000001</v>
@@ -3753,28 +3753,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M30">
-        <v>21.407904</v>
+        <v>22.172472</v>
       </c>
       <c r="N30">
-        <v>198.2487626666667</v>
+        <v>197.4841946666667</v>
       </c>
       <c r="O30">
-        <v>59.4746288</v>
+        <v>59.2452584</v>
       </c>
       <c r="P30">
-        <v>138.7741338666667</v>
+        <v>138.2389362666667</v>
       </c>
       <c r="Q30">
-        <v>142.7841338666667</v>
+        <v>142.2489362666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1230995469447697</v>
+        <v>0.1239315428064669</v>
       </c>
       <c r="T30">
-        <v>1.124802594679756</v>
+        <v>1.136909148223575</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.26054053057537</v>
+        <v>9.90672878814174</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09850679539259151</v>
+        <v>0.09858611698494882</v>
       </c>
       <c r="C31">
-        <v>1118.741850781135</v>
+        <v>1102.735813187945</v>
       </c>
       <c r="D31">
-        <v>1453.381850781135</v>
+        <v>1452.135813187944</v>
       </c>
       <c r="E31">
-        <v>91.63999999999999</v>
+        <v>106.4</v>
       </c>
       <c r="F31">
-        <v>428.04</v>
+        <v>442.8</v>
       </c>
       <c r="G31">
         <v>93.40000000000001</v>
@@ -3835,45 +3835,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M31">
-        <v>22.172472</v>
+        <v>23.6898</v>
       </c>
       <c r="N31">
-        <v>197.4841946666667</v>
+        <v>195.9668666666667</v>
       </c>
       <c r="O31">
-        <v>59.2452584</v>
+        <v>58.79006000000001</v>
       </c>
       <c r="P31">
-        <v>138.2389362666667</v>
+        <v>137.1768066666667</v>
       </c>
       <c r="Q31">
-        <v>142.2489362666667</v>
+        <v>141.1868066666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1239315428064669</v>
+        <v>0.1247873099784983</v>
       </c>
       <c r="T31">
-        <v>1.136909148223575</v>
+        <v>1.149361603297218</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.906728788141741</v>
+        <v>9.272204352365435</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09858611698494882</v>
+        <v>0.09832033857730613</v>
       </c>
       <c r="C32">
-        <v>1102.735813187945</v>
+        <v>1092.159279564351</v>
       </c>
       <c r="D32">
-        <v>1452.135813187944</v>
+        <v>1456.319279564351</v>
       </c>
       <c r="E32">
-        <v>106.4</v>
+        <v>121.16</v>
       </c>
       <c r="F32">
-        <v>442.8</v>
+        <v>457.56</v>
       </c>
       <c r="G32">
         <v>93.40000000000001</v>
@@ -3917,28 +3917,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M32">
-        <v>23.6898</v>
+        <v>24.47946</v>
       </c>
       <c r="N32">
-        <v>195.9668666666667</v>
+        <v>195.1772066666667</v>
       </c>
       <c r="O32">
-        <v>58.79006000000001</v>
+        <v>58.55316200000001</v>
       </c>
       <c r="P32">
-        <v>137.1768066666667</v>
+        <v>136.6240446666667</v>
       </c>
       <c r="Q32">
-        <v>141.1868066666667</v>
+        <v>140.6340446666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1247873099784983</v>
+        <v>0.1256678819960959</v>
       </c>
       <c r="T32">
-        <v>1.149361603297218</v>
+        <v>1.162174999097632</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.272204352365435</v>
+        <v>8.9731009861601</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09832033857730613</v>
+        <v>0.09805456016966345</v>
       </c>
       <c r="C33">
-        <v>1092.159279564351</v>
+        <v>1081.606919928197</v>
       </c>
       <c r="D33">
-        <v>1456.319279564351</v>
+        <v>1460.526919928197</v>
       </c>
       <c r="E33">
-        <v>121.16</v>
+        <v>135.92</v>
       </c>
       <c r="F33">
-        <v>457.56</v>
+        <v>472.32</v>
       </c>
       <c r="G33">
         <v>93.40000000000001</v>
@@ -3999,28 +3999,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M33">
-        <v>24.47946</v>
+        <v>25.26912</v>
       </c>
       <c r="N33">
-        <v>195.1772066666667</v>
+        <v>194.3875466666667</v>
       </c>
       <c r="O33">
-        <v>58.55316200000001</v>
+        <v>58.31626400000001</v>
       </c>
       <c r="P33">
-        <v>136.6240446666667</v>
+        <v>136.0712826666667</v>
       </c>
       <c r="Q33">
-        <v>140.6340446666667</v>
+        <v>140.0812826666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1256678819960959</v>
+        <v>0.1265743531906816</v>
       </c>
       <c r="T33">
-        <v>1.162174999097632</v>
+        <v>1.175365259480412</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.9731009861601</v>
+        <v>8.692691580342597</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09805456016966345</v>
+        <v>0.09778878176202076</v>
       </c>
       <c r="C34">
-        <v>1081.606919928197</v>
+        <v>1071.078944419205</v>
       </c>
       <c r="D34">
-        <v>1460.526919928197</v>
+        <v>1464.758944419205</v>
       </c>
       <c r="E34">
-        <v>135.92</v>
+        <v>150.6800000000001</v>
       </c>
       <c r="F34">
-        <v>472.32</v>
+        <v>487.08</v>
       </c>
       <c r="G34">
         <v>93.40000000000001</v>
@@ -4081,28 +4081,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M34">
-        <v>25.26912</v>
+        <v>26.05878</v>
       </c>
       <c r="N34">
-        <v>194.3875466666667</v>
+        <v>193.5978866666667</v>
       </c>
       <c r="O34">
-        <v>58.31626400000001</v>
+        <v>58.079366</v>
       </c>
       <c r="P34">
-        <v>136.0712826666667</v>
+        <v>135.5185206666667</v>
       </c>
       <c r="Q34">
-        <v>140.0812826666667</v>
+        <v>139.5285206666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1265743531906816</v>
+        <v>0.1275078832268967</v>
       </c>
       <c r="T34">
-        <v>1.175365259480412</v>
+        <v>1.188949258979097</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.692691580342597</v>
+        <v>8.429276683968578</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09778878176202076</v>
+        <v>0.09752300335437807</v>
       </c>
       <c r="C35">
-        <v>1071.078944419205</v>
+        <v>1060.575565619778</v>
       </c>
       <c r="D35">
-        <v>1464.758944419205</v>
+        <v>1469.015565619778</v>
       </c>
       <c r="E35">
-        <v>150.6800000000001</v>
+        <v>165.4400000000001</v>
       </c>
       <c r="F35">
-        <v>487.08</v>
+        <v>501.84</v>
       </c>
       <c r="G35">
         <v>93.40000000000001</v>
@@ -4163,28 +4163,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M35">
-        <v>26.05878</v>
+        <v>26.84844</v>
       </c>
       <c r="N35">
-        <v>193.5978866666667</v>
+        <v>192.8082266666667</v>
       </c>
       <c r="O35">
-        <v>58.079366</v>
+        <v>57.842468</v>
       </c>
       <c r="P35">
-        <v>135.5185206666667</v>
+        <v>134.9657586666667</v>
       </c>
       <c r="Q35">
-        <v>139.5285206666667</v>
+        <v>138.9757586666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1275078832268967</v>
+        <v>0.128469702052088</v>
       </c>
       <c r="T35">
-        <v>1.188949258979097</v>
+        <v>1.202944894826225</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.429276683968578</v>
+        <v>8.181356781498913</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09752300335437807</v>
+        <v>0.09725722494673536</v>
       </c>
       <c r="C36">
-        <v>1060.575565619778</v>
+        <v>1050.0969985906</v>
       </c>
       <c r="D36">
-        <v>1469.015565619778</v>
+        <v>1473.2969985906</v>
       </c>
       <c r="E36">
-        <v>165.4400000000001</v>
+        <v>180.2</v>
       </c>
       <c r="F36">
-        <v>501.84</v>
+        <v>516.6</v>
       </c>
       <c r="G36">
         <v>93.40000000000001</v>
@@ -4245,28 +4245,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M36">
-        <v>26.84844</v>
+        <v>27.6381</v>
       </c>
       <c r="N36">
-        <v>192.8082266666667</v>
+        <v>192.0185666666667</v>
       </c>
       <c r="O36">
-        <v>57.842468</v>
+        <v>57.60557</v>
       </c>
       <c r="P36">
-        <v>134.9657586666667</v>
+        <v>134.4129966666667</v>
       </c>
       <c r="Q36">
-        <v>138.9757586666667</v>
+        <v>138.4229966666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.128469702052088</v>
+        <v>0.1294611153026698</v>
       </c>
       <c r="T36">
-        <v>1.202944894826225</v>
+        <v>1.217371165622497</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.181356781498913</v>
+        <v>7.947603730598944</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09725722494673536</v>
+        <v>0.0969914465390927</v>
       </c>
       <c r="C37">
-        <v>1050.0969985906</v>
+        <v>1039.643460906849</v>
       </c>
       <c r="D37">
-        <v>1473.2969985906</v>
+        <v>1477.603460906849</v>
       </c>
       <c r="E37">
-        <v>180.2</v>
+        <v>194.96</v>
       </c>
       <c r="F37">
-        <v>516.6</v>
+        <v>531.36</v>
       </c>
       <c r="G37">
         <v>93.40000000000001</v>
@@ -4327,28 +4327,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M37">
-        <v>27.6381</v>
+        <v>28.42776</v>
       </c>
       <c r="N37">
-        <v>192.0185666666667</v>
+        <v>191.2289066666667</v>
       </c>
       <c r="O37">
-        <v>57.60557</v>
+        <v>57.368672</v>
       </c>
       <c r="P37">
-        <v>134.4129966666667</v>
+        <v>133.8602346666667</v>
       </c>
       <c r="Q37">
-        <v>138.4229966666667</v>
+        <v>137.8702346666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1294611153026698</v>
+        <v>0.1304835102173323</v>
       </c>
       <c r="T37">
-        <v>1.217371165622497</v>
+        <v>1.232248257381152</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.947603730598944</v>
+        <v>7.72683696030453</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0969914465390927</v>
+        <v>0.09693286813145001</v>
       </c>
       <c r="C38">
-        <v>1039.643460906849</v>
+        <v>1025.836006986644</v>
       </c>
       <c r="D38">
-        <v>1477.603460906849</v>
+        <v>1478.556006986644</v>
       </c>
       <c r="E38">
-        <v>194.96</v>
+        <v>209.72</v>
       </c>
       <c r="F38">
-        <v>531.36</v>
+        <v>546.12</v>
       </c>
       <c r="G38">
         <v>93.40000000000001</v>
@@ -4409,45 +4409,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M38">
-        <v>28.42776</v>
+        <v>29.654316</v>
       </c>
       <c r="N38">
-        <v>191.2289066666667</v>
+        <v>190.0023506666667</v>
       </c>
       <c r="O38">
-        <v>57.368672</v>
+        <v>57.00070520000001</v>
       </c>
       <c r="P38">
-        <v>133.8602346666667</v>
+        <v>133.0016454666667</v>
       </c>
       <c r="Q38">
-        <v>137.8702346666667</v>
+        <v>137.0116454666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1304835102173323</v>
+        <v>0.1315383621134127</v>
       </c>
       <c r="T38">
-        <v>1.232248257381152</v>
+        <v>1.247597637767065</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.72683696030453</v>
+        <v>7.407241046013898</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09693286813145001</v>
+        <v>0.09667268972380731</v>
       </c>
       <c r="C39">
-        <v>1025.836006986644</v>
+        <v>1015.321663430305</v>
       </c>
       <c r="D39">
-        <v>1478.556006986644</v>
+        <v>1482.801663430304</v>
       </c>
       <c r="E39">
-        <v>209.72</v>
+        <v>224.48</v>
       </c>
       <c r="F39">
-        <v>546.12</v>
+        <v>560.88</v>
       </c>
       <c r="G39">
         <v>93.40000000000001</v>
@@ -4491,28 +4491,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M39">
-        <v>29.654316</v>
+        <v>30.455784</v>
       </c>
       <c r="N39">
-        <v>190.0023506666667</v>
+        <v>189.2008826666667</v>
       </c>
       <c r="O39">
-        <v>57.00070520000001</v>
+        <v>56.76026480000001</v>
       </c>
       <c r="P39">
-        <v>133.0016454666667</v>
+        <v>132.4406178666667</v>
       </c>
       <c r="Q39">
-        <v>137.0116454666667</v>
+        <v>136.4506178666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1315383621134127</v>
+        <v>0.1326272414900118</v>
       </c>
       <c r="T39">
-        <v>1.247597637767065</v>
+        <v>1.26344215945575</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.407241046013898</v>
+        <v>7.212313650066164</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09667268972380731</v>
+        <v>0.09641251131616464</v>
       </c>
       <c r="C40">
-        <v>1015.321663430305</v>
+        <v>1004.831772796826</v>
       </c>
       <c r="D40">
-        <v>1482.801663430304</v>
+        <v>1487.071772796826</v>
       </c>
       <c r="E40">
-        <v>224.48</v>
+        <v>239.24</v>
       </c>
       <c r="F40">
-        <v>560.88</v>
+        <v>575.64</v>
       </c>
       <c r="G40">
         <v>93.40000000000001</v>
@@ -4573,28 +4573,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M40">
-        <v>30.455784</v>
+        <v>31.257252</v>
       </c>
       <c r="N40">
-        <v>189.2008826666667</v>
+        <v>188.3994146666667</v>
       </c>
       <c r="O40">
-        <v>56.76026480000001</v>
+        <v>56.51982440000001</v>
       </c>
       <c r="P40">
-        <v>132.4406178666667</v>
+        <v>131.8795902666667</v>
       </c>
       <c r="Q40">
-        <v>136.4506178666667</v>
+        <v>135.8895902666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1326272414900118</v>
+        <v>0.1337518218297781</v>
       </c>
       <c r="T40">
-        <v>1.26344215945575</v>
+        <v>1.279806173658819</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.212313650066164</v>
+        <v>7.027382530833699</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09641251131616464</v>
+        <v>0.09615233290852195</v>
       </c>
       <c r="C41">
-        <v>1004.831772796826</v>
+        <v>994.3665469518022</v>
       </c>
       <c r="D41">
-        <v>1487.071772796826</v>
+        <v>1491.366546951802</v>
       </c>
       <c r="E41">
-        <v>239.24</v>
+        <v>254</v>
       </c>
       <c r="F41">
-        <v>575.64</v>
+        <v>590.4</v>
       </c>
       <c r="G41">
         <v>93.40000000000001</v>
@@ -4655,28 +4655,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M41">
-        <v>31.257252</v>
+        <v>32.05872</v>
       </c>
       <c r="N41">
-        <v>188.3994146666667</v>
+        <v>187.5979466666667</v>
       </c>
       <c r="O41">
-        <v>56.51982440000001</v>
+        <v>56.27938400000001</v>
       </c>
       <c r="P41">
-        <v>131.8795902666667</v>
+        <v>131.3185626666667</v>
       </c>
       <c r="Q41">
-        <v>135.8895902666667</v>
+        <v>135.3285626666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1337518218297781</v>
+        <v>0.1349138881808699</v>
       </c>
       <c r="T41">
-        <v>1.279806173658819</v>
+        <v>1.296715655001989</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.027382530833699</v>
+        <v>6.851697967562856</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09615233290852195</v>
+        <v>0.09589215450087925</v>
       </c>
       <c r="C42">
-        <v>994.3665469518022</v>
+        <v>983.9262002154496</v>
       </c>
       <c r="D42">
-        <v>1491.366546951802</v>
+        <v>1495.68620021545</v>
       </c>
       <c r="E42">
-        <v>254</v>
+        <v>268.7600000000001</v>
       </c>
       <c r="F42">
-        <v>590.4</v>
+        <v>605.1600000000001</v>
       </c>
       <c r="G42">
         <v>93.40000000000001</v>
@@ -4737,28 +4737,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M42">
-        <v>32.05872</v>
+        <v>32.86018800000001</v>
       </c>
       <c r="N42">
-        <v>187.5979466666667</v>
+        <v>186.7964786666667</v>
       </c>
       <c r="O42">
-        <v>56.27938400000001</v>
+        <v>56.03894360000001</v>
       </c>
       <c r="P42">
-        <v>131.3185626666667</v>
+        <v>130.7575350666667</v>
       </c>
       <c r="Q42">
-        <v>135.3285626666667</v>
+        <v>134.7675350666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1349138881808699</v>
+        <v>0.1361153466116597</v>
       </c>
       <c r="T42">
-        <v>1.296715655001989</v>
+        <v>1.314198339102555</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.851697967562856</v>
+        <v>6.684583382988151</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09589215450087925</v>
+        <v>0.09563197609323656</v>
       </c>
       <c r="C43">
-        <v>983.9262002154496</v>
+        <v>973.5109493982602</v>
       </c>
       <c r="D43">
-        <v>1495.68620021545</v>
+        <v>1500.03094939826</v>
       </c>
       <c r="E43">
-        <v>268.7600000000001</v>
+        <v>283.5200000000001</v>
       </c>
       <c r="F43">
-        <v>605.1600000000001</v>
+        <v>619.9200000000001</v>
       </c>
       <c r="G43">
         <v>93.40000000000001</v>
@@ -4819,28 +4819,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M43">
-        <v>32.86018800000001</v>
+        <v>33.66165600000001</v>
       </c>
       <c r="N43">
-        <v>186.7964786666667</v>
+        <v>185.9950106666667</v>
       </c>
       <c r="O43">
-        <v>56.03894360000001</v>
+        <v>55.79850320000001</v>
       </c>
       <c r="P43">
-        <v>130.7575350666667</v>
+        <v>130.1965074666667</v>
       </c>
       <c r="Q43">
-        <v>134.7675350666667</v>
+        <v>134.2065074666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1361153466116597</v>
+        <v>0.1373582346435113</v>
       </c>
       <c r="T43">
-        <v>1.314198339102555</v>
+        <v>1.332283874379003</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.684583382988151</v>
+        <v>6.525426635774147</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09563197609323656</v>
+        <v>0.09537179768559387</v>
       </c>
       <c r="C44">
-        <v>973.5109493982603</v>
+        <v>963.121013837277</v>
       </c>
       <c r="D44">
-        <v>1500.03094939826</v>
+        <v>1504.401013837277</v>
       </c>
       <c r="E44">
-        <v>283.52</v>
+        <v>298.28</v>
       </c>
       <c r="F44">
-        <v>619.92</v>
+        <v>634.6799999999999</v>
       </c>
       <c r="G44">
         <v>93.40000000000001</v>
@@ -4901,28 +4901,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M44">
-        <v>33.661656</v>
+        <v>34.463124</v>
       </c>
       <c r="N44">
-        <v>185.9950106666667</v>
+        <v>185.1935426666667</v>
       </c>
       <c r="O44">
-        <v>55.79850320000001</v>
+        <v>55.55806280000001</v>
       </c>
       <c r="P44">
-        <v>130.1965074666667</v>
+        <v>129.6354798666667</v>
       </c>
       <c r="Q44">
-        <v>134.2065074666667</v>
+        <v>133.6454798666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1373582346435113</v>
+        <v>0.1386447327817436</v>
       </c>
       <c r="T44">
-        <v>1.332283874379003</v>
+        <v>1.351003989840589</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.525426635774149</v>
+        <v>6.373672527965448</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09537179768559387</v>
+        <v>0.0951116192779512</v>
       </c>
       <c r="C45">
-        <v>963.121013837277</v>
+        <v>952.756615433002</v>
       </c>
       <c r="D45">
-        <v>1504.401013837277</v>
+        <v>1508.796615433002</v>
       </c>
       <c r="E45">
-        <v>298.28</v>
+        <v>313.0400000000001</v>
       </c>
       <c r="F45">
-        <v>634.6799999999999</v>
+        <v>649.4400000000001</v>
       </c>
       <c r="G45">
         <v>93.40000000000001</v>
@@ -4983,28 +4983,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M45">
-        <v>34.463124</v>
+        <v>35.264592</v>
       </c>
       <c r="N45">
-        <v>185.1935426666667</v>
+        <v>184.3920746666667</v>
       </c>
       <c r="O45">
-        <v>55.55806280000001</v>
+        <v>55.31762240000001</v>
       </c>
       <c r="P45">
-        <v>129.6354798666667</v>
+        <v>129.0744522666667</v>
       </c>
       <c r="Q45">
-        <v>133.6454798666667</v>
+        <v>133.0844522666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1386447327817436</v>
+        <v>0.1399771772820557</v>
       </c>
       <c r="T45">
-        <v>1.351003989840589</v>
+        <v>1.370392680854375</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.373672527965448</v>
+        <v>6.228816334148052</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0951116192779512</v>
+        <v>0.09516644087030852</v>
       </c>
       <c r="C46">
-        <v>952.756615433002</v>
+        <v>937.0682937192707</v>
       </c>
       <c r="D46">
-        <v>1508.796615433002</v>
+        <v>1507.868293719271</v>
       </c>
       <c r="E46">
-        <v>313.0400000000001</v>
+        <v>327.8000000000001</v>
       </c>
       <c r="F46">
-        <v>649.4400000000001</v>
+        <v>664.2</v>
       </c>
       <c r="G46">
         <v>93.40000000000001</v>
@@ -5065,45 +5065,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M46">
-        <v>35.264592</v>
+        <v>36.73026</v>
       </c>
       <c r="N46">
-        <v>184.3920746666667</v>
+        <v>182.9264066666667</v>
       </c>
       <c r="O46">
-        <v>55.31762240000001</v>
+        <v>54.87792200000001</v>
       </c>
       <c r="P46">
-        <v>129.0744522666667</v>
+        <v>128.0484846666667</v>
       </c>
       <c r="Q46">
-        <v>133.0844522666667</v>
+        <v>132.0584846666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1399771772820557</v>
+        <v>0.1413580743096518</v>
       </c>
       <c r="T46">
-        <v>1.370392680854375</v>
+        <v>1.390486415177753</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.228816334148052</v>
+        <v>5.980264410506941</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09516644087030852</v>
+        <v>0.09491326246266582</v>
       </c>
       <c r="C47">
-        <v>937.0682937192707</v>
+        <v>926.6050629130698</v>
       </c>
       <c r="D47">
-        <v>1507.868293719271</v>
+        <v>1512.16506291307</v>
       </c>
       <c r="E47">
-        <v>327.8000000000001</v>
+        <v>342.5600000000001</v>
       </c>
       <c r="F47">
-        <v>664.2</v>
+        <v>678.96</v>
       </c>
       <c r="G47">
         <v>93.40000000000001</v>
@@ -5147,28 +5147,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M47">
-        <v>36.73026</v>
+        <v>37.546488</v>
       </c>
       <c r="N47">
-        <v>182.9264066666667</v>
+        <v>182.1101786666667</v>
       </c>
       <c r="O47">
-        <v>54.87792200000001</v>
+        <v>54.6330536</v>
       </c>
       <c r="P47">
-        <v>128.0484846666667</v>
+        <v>127.4771250666667</v>
       </c>
       <c r="Q47">
-        <v>132.0584846666667</v>
+        <v>131.4871250666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1413580743096518</v>
+        <v>0.1427901156716034</v>
       </c>
       <c r="T47">
-        <v>1.390486415177753</v>
+        <v>1.411324361883478</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.980264410506941</v>
+        <v>5.850258662452442</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09491326246266582</v>
+        <v>0.09466008405502313</v>
       </c>
       <c r="C48">
-        <v>926.6050629130698</v>
+        <v>916.1663899349514</v>
       </c>
       <c r="D48">
-        <v>1512.16506291307</v>
+        <v>1516.486389934951</v>
       </c>
       <c r="E48">
-        <v>342.5600000000001</v>
+        <v>357.3200000000001</v>
       </c>
       <c r="F48">
-        <v>678.96</v>
+        <v>693.72</v>
       </c>
       <c r="G48">
         <v>93.40000000000001</v>
@@ -5229,28 +5229,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M48">
-        <v>37.546488</v>
+        <v>38.36271600000001</v>
       </c>
       <c r="N48">
-        <v>182.1101786666667</v>
+        <v>181.2939506666667</v>
       </c>
       <c r="O48">
-        <v>54.6330536</v>
+        <v>54.3881852</v>
       </c>
       <c r="P48">
-        <v>127.4771250666667</v>
+        <v>126.9057654666667</v>
       </c>
       <c r="Q48">
-        <v>131.4871250666667</v>
+        <v>130.9157654666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1427901156716034</v>
+        <v>0.1442761963302323</v>
       </c>
       <c r="T48">
-        <v>1.411324361883478</v>
+        <v>1.43294864620074</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.850258662452442</v>
+        <v>5.725785073889624</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09466008405502313</v>
+        <v>0.09440690564738044</v>
       </c>
       <c r="C49">
-        <v>916.1663899349514</v>
+        <v>905.7524859256398</v>
       </c>
       <c r="D49">
-        <v>1516.486389934951</v>
+        <v>1520.83248592564</v>
       </c>
       <c r="E49">
-        <v>357.3200000000001</v>
+        <v>372.08</v>
       </c>
       <c r="F49">
-        <v>693.72</v>
+        <v>708.48</v>
       </c>
       <c r="G49">
         <v>93.40000000000001</v>
@@ -5311,28 +5311,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M49">
-        <v>38.36271600000001</v>
+        <v>39.178944</v>
       </c>
       <c r="N49">
-        <v>181.2939506666667</v>
+        <v>180.4777226666667</v>
       </c>
       <c r="O49">
-        <v>54.3881852</v>
+        <v>54.14331680000001</v>
       </c>
       <c r="P49">
-        <v>126.9057654666667</v>
+        <v>126.3344058666667</v>
       </c>
       <c r="Q49">
-        <v>130.9157654666667</v>
+        <v>130.3444058666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1442761963302323</v>
+        <v>0.1458194339372701</v>
       </c>
       <c r="T49">
-        <v>1.43294864620074</v>
+        <v>1.455404633760974</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.725785073889624</v>
+        <v>5.606497884850257</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09440690564738044</v>
+        <v>0.09415372723973774</v>
       </c>
       <c r="C50">
-        <v>905.7524859256398</v>
+        <v>895.363564453248</v>
       </c>
       <c r="D50">
-        <v>1520.83248592564</v>
+        <v>1525.203564453248</v>
       </c>
       <c r="E50">
-        <v>372.08</v>
+        <v>386.84</v>
       </c>
       <c r="F50">
-        <v>708.48</v>
+        <v>723.24</v>
       </c>
       <c r="G50">
         <v>93.40000000000001</v>
@@ -5393,28 +5393,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M50">
-        <v>39.178944</v>
+        <v>39.995172</v>
       </c>
       <c r="N50">
-        <v>180.4777226666667</v>
+        <v>179.6614946666667</v>
       </c>
       <c r="O50">
-        <v>54.14331680000001</v>
+        <v>53.89844840000001</v>
       </c>
       <c r="P50">
-        <v>126.3344058666667</v>
+        <v>125.7630462666667</v>
       </c>
       <c r="Q50">
-        <v>130.3444058666667</v>
+        <v>129.7730462666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1458194339372701</v>
+        <v>0.1474231906661524</v>
       </c>
       <c r="T50">
-        <v>1.455404633760974</v>
+        <v>1.478741248284354</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.606497884850257</v>
+        <v>5.49207956066964</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09415372723973774</v>
+        <v>0.09390054883209506</v>
       </c>
       <c r="C51">
-        <v>895.363564453248</v>
+        <v>884.9998415482589</v>
       </c>
       <c r="D51">
-        <v>1525.203564453248</v>
+        <v>1529.599841548259</v>
       </c>
       <c r="E51">
-        <v>386.84</v>
+        <v>401.6</v>
       </c>
       <c r="F51">
-        <v>723.24</v>
+        <v>738</v>
       </c>
       <c r="G51">
         <v>93.40000000000001</v>
@@ -5475,28 +5475,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M51">
-        <v>39.995172</v>
+        <v>40.8114</v>
       </c>
       <c r="N51">
-        <v>179.6614946666667</v>
+        <v>178.8452666666667</v>
       </c>
       <c r="O51">
-        <v>53.89844840000001</v>
+        <v>53.65358000000001</v>
       </c>
       <c r="P51">
-        <v>125.7630462666667</v>
+        <v>125.1916866666667</v>
       </c>
       <c r="Q51">
-        <v>129.7730462666667</v>
+        <v>129.2016866666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1474231906661524</v>
+        <v>0.1490910976641901</v>
       </c>
       <c r="T51">
-        <v>1.478741248284354</v>
+        <v>1.503011327388669</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.49207956066964</v>
+        <v>5.382237969456248</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09390054883209506</v>
+        <v>0.09364737042445238</v>
       </c>
       <c r="C52">
-        <v>884.9998415482589</v>
+        <v>874.6615357391197</v>
       </c>
       <c r="D52">
-        <v>1529.599841548259</v>
+        <v>1534.02153573912</v>
       </c>
       <c r="E52">
-        <v>401.6</v>
+        <v>416.36</v>
       </c>
       <c r="F52">
-        <v>738</v>
+        <v>752.76</v>
       </c>
       <c r="G52">
         <v>93.40000000000001</v>
@@ -5557,28 +5557,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M52">
-        <v>40.8114</v>
+        <v>41.627628</v>
       </c>
       <c r="N52">
-        <v>178.8452666666667</v>
+        <v>178.0290386666667</v>
       </c>
       <c r="O52">
-        <v>53.65358000000001</v>
+        <v>53.4087116</v>
       </c>
       <c r="P52">
-        <v>125.1916866666667</v>
+        <v>124.6203270666667</v>
       </c>
       <c r="Q52">
-        <v>129.2016866666667</v>
+        <v>128.6303270666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1490910976641901</v>
+        <v>0.1508270824988824</v>
       </c>
       <c r="T52">
-        <v>1.503011327388669</v>
+        <v>1.52827202196663</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.382237969456248</v>
+        <v>5.276703891623772</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09364737042445238</v>
+        <v>0.09339419201680968</v>
       </c>
       <c r="C53">
-        <v>874.6615357391197</v>
+        <v>864.3488680884502</v>
       </c>
       <c r="D53">
-        <v>1534.02153573912</v>
+        <v>1538.46886808845</v>
       </c>
       <c r="E53">
-        <v>416.36</v>
+        <v>431.12</v>
       </c>
       <c r="F53">
-        <v>752.76</v>
+        <v>767.52</v>
       </c>
       <c r="G53">
         <v>93.40000000000001</v>
@@ -5639,28 +5639,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M53">
-        <v>41.627628</v>
+        <v>42.443856</v>
       </c>
       <c r="N53">
-        <v>178.0290386666667</v>
+        <v>177.2128106666667</v>
       </c>
       <c r="O53">
-        <v>53.4087116</v>
+        <v>53.1638432</v>
       </c>
       <c r="P53">
-        <v>124.6203270666667</v>
+        <v>124.0489674666667</v>
       </c>
       <c r="Q53">
-        <v>128.6303270666667</v>
+        <v>128.0589674666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1508270824988824</v>
+        <v>0.1526354000350202</v>
       </c>
       <c r="T53">
-        <v>1.52827202196663</v>
+        <v>1.554585245485339</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.276703891623772</v>
+        <v>5.175228816784853</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09339419201680968</v>
+        <v>0.09314101360916699</v>
       </c>
       <c r="C54">
-        <v>864.3488680884502</v>
+        <v>854.0620622298808</v>
       </c>
       <c r="D54">
-        <v>1538.46886808845</v>
+        <v>1542.942062229881</v>
       </c>
       <c r="E54">
-        <v>431.12</v>
+        <v>445.8800000000001</v>
       </c>
       <c r="F54">
-        <v>767.52</v>
+        <v>782.2800000000001</v>
       </c>
       <c r="G54">
         <v>93.40000000000001</v>
@@ -5721,28 +5721,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M54">
-        <v>42.443856</v>
+        <v>43.26008400000001</v>
       </c>
       <c r="N54">
-        <v>177.2128106666667</v>
+        <v>176.3965826666667</v>
       </c>
       <c r="O54">
-        <v>53.1638432</v>
+        <v>52.91897480000001</v>
       </c>
       <c r="P54">
-        <v>124.0489674666667</v>
+        <v>123.4776078666667</v>
       </c>
       <c r="Q54">
-        <v>128.0589674666667</v>
+        <v>127.4876078666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1526354000350202</v>
+        <v>0.1545206672535468</v>
       </c>
       <c r="T54">
-        <v>1.554585245485339</v>
+        <v>1.582018180643142</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.175228816784853</v>
+        <v>5.077582990053063</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09314101360916699</v>
+        <v>0.09288783520152431</v>
       </c>
       <c r="C55">
-        <v>854.0620622298808</v>
+        <v>843.8013444055435</v>
       </c>
       <c r="D55">
-        <v>1542.942062229881</v>
+        <v>1547.441344405544</v>
       </c>
       <c r="E55">
-        <v>445.8800000000001</v>
+        <v>460.6400000000001</v>
       </c>
       <c r="F55">
-        <v>782.2800000000001</v>
+        <v>797.0400000000001</v>
       </c>
       <c r="G55">
         <v>93.40000000000001</v>
@@ -5803,28 +5803,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M55">
-        <v>43.26008400000001</v>
+        <v>44.07631200000001</v>
       </c>
       <c r="N55">
-        <v>176.3965826666667</v>
+        <v>175.5803546666667</v>
       </c>
       <c r="O55">
-        <v>52.91897480000001</v>
+        <v>52.67410640000001</v>
       </c>
       <c r="P55">
-        <v>123.4776078666667</v>
+        <v>122.9062482666667</v>
       </c>
       <c r="Q55">
-        <v>127.4876078666667</v>
+        <v>126.9162482666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1545206672535468</v>
+        <v>0.1564879026120094</v>
       </c>
       <c r="T55">
-        <v>1.582018180643142</v>
+        <v>1.610643852112154</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.077582990053063</v>
+        <v>4.983553675422451</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09288783520152431</v>
+        <v>0.09263465679388161</v>
       </c>
       <c r="C56">
-        <v>843.8013444055435</v>
+        <v>833.5669435042131</v>
       </c>
       <c r="D56">
-        <v>1547.441344405544</v>
+        <v>1551.966943504213</v>
       </c>
       <c r="E56">
-        <v>460.6400000000001</v>
+        <v>475.4000000000001</v>
       </c>
       <c r="F56">
-        <v>797.0400000000001</v>
+        <v>811.8000000000001</v>
       </c>
       <c r="G56">
         <v>93.40000000000001</v>
@@ -5885,28 +5885,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M56">
-        <v>44.07631200000001</v>
+        <v>44.89254</v>
       </c>
       <c r="N56">
-        <v>175.5803546666667</v>
+        <v>174.7641266666667</v>
       </c>
       <c r="O56">
-        <v>52.67410640000001</v>
+        <v>52.42923800000001</v>
       </c>
       <c r="P56">
-        <v>122.9062482666667</v>
+        <v>122.3348886666667</v>
       </c>
       <c r="Q56">
-        <v>126.9162482666667</v>
+        <v>126.3448886666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1564879026120094</v>
+        <v>0.1585425706530703</v>
       </c>
       <c r="T56">
-        <v>1.610643852112154</v>
+        <v>1.640541775646456</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.983553675422451</v>
+        <v>4.892943608596588</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09263465679388161</v>
+        <v>0.09238147838623892</v>
       </c>
       <c r="C57">
-        <v>833.5669435042131</v>
+        <v>823.359091100121</v>
       </c>
       <c r="D57">
-        <v>1551.966943504213</v>
+        <v>1556.519091100121</v>
       </c>
       <c r="E57">
-        <v>475.4000000000001</v>
+        <v>490.1600000000001</v>
       </c>
       <c r="F57">
-        <v>811.8000000000001</v>
+        <v>826.5600000000001</v>
       </c>
       <c r="G57">
         <v>93.40000000000001</v>
@@ -5967,28 +5967,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M57">
-        <v>44.89254</v>
+        <v>45.70876800000001</v>
       </c>
       <c r="N57">
-        <v>174.7641266666667</v>
+        <v>173.9478986666667</v>
       </c>
       <c r="O57">
-        <v>52.42923800000001</v>
+        <v>52.1843696</v>
       </c>
       <c r="P57">
-        <v>122.3348886666667</v>
+        <v>121.7635290666667</v>
       </c>
       <c r="Q57">
-        <v>126.3448886666667</v>
+        <v>125.7735290666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1585425706530703</v>
+        <v>0.1606906326959976</v>
       </c>
       <c r="T57">
-        <v>1.640541775646456</v>
+        <v>1.671798695705044</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.892943608596588</v>
+        <v>4.805569615585934</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09238147838623892</v>
+        <v>0.09212829997859624</v>
       </c>
       <c r="C58">
-        <v>823.359091100121</v>
+        <v>813.1780214924576</v>
       </c>
       <c r="D58">
-        <v>1556.519091100121</v>
+        <v>1561.098021492458</v>
       </c>
       <c r="E58">
-        <v>490.1600000000001</v>
+        <v>504.9200000000001</v>
       </c>
       <c r="F58">
-        <v>826.5600000000001</v>
+        <v>841.3200000000001</v>
       </c>
       <c r="G58">
         <v>93.40000000000001</v>
@@ -6049,28 +6049,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M58">
-        <v>45.70876800000001</v>
+        <v>46.524996</v>
       </c>
       <c r="N58">
-        <v>173.9478986666667</v>
+        <v>173.1316706666667</v>
       </c>
       <c r="O58">
-        <v>52.1843696</v>
+        <v>51.93950120000001</v>
       </c>
       <c r="P58">
-        <v>121.7635290666667</v>
+        <v>121.1921694666667</v>
       </c>
       <c r="Q58">
-        <v>125.7735290666667</v>
+        <v>125.2021694666667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1606906326959976</v>
+        <v>0.1629386046013866</v>
       </c>
       <c r="T58">
-        <v>1.671798695705044</v>
+        <v>1.704509425998915</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.805569615585934</v>
+        <v>4.721261376716006</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09212829997859624</v>
+        <v>0.09187512157095355</v>
       </c>
       <c r="C59">
-        <v>813.1780214924576</v>
+        <v>803.0239717455711</v>
       </c>
       <c r="D59">
-        <v>1561.098021492458</v>
+        <v>1565.703971745571</v>
       </c>
       <c r="E59">
-        <v>504.9200000000001</v>
+        <v>519.6800000000002</v>
       </c>
       <c r="F59">
-        <v>841.3200000000001</v>
+        <v>856.0800000000002</v>
       </c>
       <c r="G59">
         <v>93.40000000000001</v>
@@ -6131,28 +6131,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M59">
-        <v>46.524996</v>
+        <v>47.34122400000001</v>
       </c>
       <c r="N59">
-        <v>173.1316706666667</v>
+        <v>172.3154426666667</v>
       </c>
       <c r="O59">
-        <v>51.93950120000001</v>
+        <v>51.6946328</v>
       </c>
       <c r="P59">
-        <v>121.1921694666667</v>
+        <v>120.6208098666667</v>
       </c>
       <c r="Q59">
-        <v>125.2021694666667</v>
+        <v>124.6308098666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1629386046013866</v>
+        <v>0.1652936227879847</v>
       </c>
       <c r="T59">
-        <v>1.704509425998915</v>
+        <v>1.738777810116304</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.721261376716006</v>
+        <v>4.639860318496764</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09187512157095354</v>
+        <v>0.09162194316331085</v>
       </c>
       <c r="C60">
-        <v>803.0239717455713</v>
+        <v>792.8971817298791</v>
       </c>
       <c r="D60">
-        <v>1565.703971745571</v>
+        <v>1570.337181729879</v>
       </c>
       <c r="E60">
-        <v>519.6799999999999</v>
+        <v>534.4399999999999</v>
       </c>
       <c r="F60">
-        <v>856.0799999999999</v>
+        <v>870.8399999999999</v>
       </c>
       <c r="G60">
         <v>93.40000000000001</v>
@@ -6213,28 +6213,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M60">
-        <v>47.341224</v>
+        <v>48.157452</v>
       </c>
       <c r="N60">
-        <v>172.3154426666667</v>
+        <v>171.4992146666667</v>
       </c>
       <c r="O60">
-        <v>51.6946328</v>
+        <v>51.44976440000001</v>
       </c>
       <c r="P60">
-        <v>120.6208098666667</v>
+        <v>120.0494502666667</v>
       </c>
       <c r="Q60">
-        <v>124.6308098666667</v>
+        <v>124.0594502666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1652936227879846</v>
+        <v>0.1677635199105143</v>
       </c>
       <c r="T60">
-        <v>1.738777810116303</v>
+        <v>1.774717822727223</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.639860318496766</v>
+        <v>4.56121861818326</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09162194316331085</v>
+        <v>0.09241876475566818</v>
       </c>
       <c r="C61">
-        <v>792.8971817298791</v>
+        <v>763.6470061183473</v>
       </c>
       <c r="D61">
-        <v>1570.337181729879</v>
+        <v>1555.847006118347</v>
       </c>
       <c r="E61">
-        <v>534.4399999999999</v>
+        <v>549.2</v>
       </c>
       <c r="F61">
-        <v>870.8399999999999</v>
+        <v>885.6</v>
       </c>
       <c r="G61">
         <v>93.40000000000001</v>
@@ -6295,45 +6295,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M61">
-        <v>48.157452</v>
+        <v>51.18768000000001</v>
       </c>
       <c r="N61">
-        <v>171.4992146666667</v>
+        <v>168.4689866666667</v>
       </c>
       <c r="O61">
-        <v>51.44976440000001</v>
+        <v>50.540696</v>
       </c>
       <c r="P61">
-        <v>120.0494502666667</v>
+        <v>117.9282906666667</v>
       </c>
       <c r="Q61">
-        <v>124.0594502666667</v>
+        <v>121.9382906666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1677635199105143</v>
+        <v>0.1703569118891704</v>
       </c>
       <c r="T61">
-        <v>1.774717822727223</v>
+        <v>1.812454835968689</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.56121861818326</v>
+        <v>4.29120184127639</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09241876475566818</v>
+        <v>0.09218308634802548</v>
       </c>
       <c r="C62">
-        <v>763.6470061183473</v>
+        <v>753.1448843054828</v>
       </c>
       <c r="D62">
-        <v>1555.847006118347</v>
+        <v>1560.104884305483</v>
       </c>
       <c r="E62">
-        <v>549.2</v>
+        <v>563.96</v>
       </c>
       <c r="F62">
-        <v>885.6</v>
+        <v>900.36</v>
       </c>
       <c r="G62">
         <v>93.40000000000001</v>
@@ -6377,28 +6377,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M62">
-        <v>51.18768000000001</v>
+        <v>52.04080800000001</v>
       </c>
       <c r="N62">
-        <v>168.4689866666667</v>
+        <v>167.6158586666667</v>
       </c>
       <c r="O62">
-        <v>50.540696</v>
+        <v>50.28475760000001</v>
       </c>
       <c r="P62">
-        <v>117.9282906666667</v>
+        <v>117.3311010666667</v>
       </c>
       <c r="Q62">
-        <v>121.9382906666667</v>
+        <v>121.3411010666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1703569118891704</v>
+        <v>0.1730832983282705</v>
       </c>
       <c r="T62">
-        <v>1.812454835968689</v>
+        <v>1.852127080658435</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.29120184127639</v>
+        <v>4.220854270107925</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09218308634802548</v>
+        <v>0.09194740794038279</v>
       </c>
       <c r="C63">
-        <v>753.1448843054828</v>
+        <v>742.6661314713377</v>
       </c>
       <c r="D63">
-        <v>1560.104884305483</v>
+        <v>1564.386131471338</v>
       </c>
       <c r="E63">
-        <v>563.96</v>
+        <v>578.72</v>
       </c>
       <c r="F63">
-        <v>900.36</v>
+        <v>915.12</v>
       </c>
       <c r="G63">
         <v>93.40000000000001</v>
@@ -6459,28 +6459,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M63">
-        <v>52.04080800000001</v>
+        <v>52.893936</v>
       </c>
       <c r="N63">
-        <v>167.6158586666667</v>
+        <v>166.7627306666667</v>
       </c>
       <c r="O63">
-        <v>50.28475760000001</v>
+        <v>50.02881920000001</v>
       </c>
       <c r="P63">
-        <v>117.3311010666667</v>
+        <v>116.7339114666667</v>
       </c>
       <c r="Q63">
-        <v>121.3411010666667</v>
+        <v>120.7439114666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1730832983282705</v>
+        <v>0.175953178790481</v>
       </c>
       <c r="T63">
-        <v>1.852127080658435</v>
+        <v>1.893887338226589</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.220854270107925</v>
+        <v>4.152775975428765</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09194740794038279</v>
+        <v>0.09171172953274012</v>
       </c>
       <c r="C64">
-        <v>742.6661314713377</v>
+        <v>732.2109405331011</v>
       </c>
       <c r="D64">
-        <v>1564.386131471338</v>
+        <v>1568.690940533101</v>
       </c>
       <c r="E64">
-        <v>578.72</v>
+        <v>593.48</v>
       </c>
       <c r="F64">
-        <v>915.12</v>
+        <v>929.88</v>
       </c>
       <c r="G64">
         <v>93.40000000000001</v>
@@ -6541,28 +6541,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M64">
-        <v>52.893936</v>
+        <v>53.747064</v>
       </c>
       <c r="N64">
-        <v>166.7627306666667</v>
+        <v>165.9096026666667</v>
       </c>
       <c r="O64">
-        <v>50.02881920000001</v>
+        <v>49.77288080000001</v>
       </c>
       <c r="P64">
-        <v>116.7339114666667</v>
+        <v>116.1367218666667</v>
       </c>
       <c r="Q64">
-        <v>120.7439114666667</v>
+        <v>120.1467218666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.175953178790481</v>
+        <v>0.1789781879263246</v>
       </c>
       <c r="T64">
-        <v>1.893887338226589</v>
+        <v>1.937904907014643</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.152775975428765</v>
+        <v>4.086858896453705</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09171172953274012</v>
+        <v>0.09147605112509742</v>
       </c>
       <c r="C65">
-        <v>732.2109405331011</v>
+        <v>721.7795065372651</v>
       </c>
       <c r="D65">
-        <v>1568.690940533101</v>
+        <v>1573.019506537265</v>
       </c>
       <c r="E65">
-        <v>593.48</v>
+        <v>608.24</v>
       </c>
       <c r="F65">
-        <v>929.88</v>
+        <v>944.64</v>
       </c>
       <c r="G65">
         <v>93.40000000000001</v>
@@ -6623,28 +6623,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M65">
-        <v>53.747064</v>
+        <v>54.600192</v>
       </c>
       <c r="N65">
-        <v>165.9096026666667</v>
+        <v>165.0564746666667</v>
       </c>
       <c r="O65">
-        <v>49.77288080000001</v>
+        <v>49.51694240000001</v>
       </c>
       <c r="P65">
-        <v>116.1367218666667</v>
+        <v>115.5395322666667</v>
       </c>
       <c r="Q65">
-        <v>120.1467218666667</v>
+        <v>119.5495322666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1789781879263246</v>
+        <v>0.1821712531252706</v>
       </c>
       <c r="T65">
-        <v>1.937904907014643</v>
+        <v>1.984367896290923</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.086858896453705</v>
+        <v>4.023001726196616</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09147605112509742</v>
+        <v>0.09283287271745473</v>
       </c>
       <c r="C66">
-        <v>721.7795065372651</v>
+        <v>682.4215620405215</v>
       </c>
       <c r="D66">
-        <v>1573.019506537265</v>
+        <v>1548.421562040521</v>
       </c>
       <c r="E66">
-        <v>608.24</v>
+        <v>623</v>
       </c>
       <c r="F66">
-        <v>944.64</v>
+        <v>959.4</v>
       </c>
       <c r="G66">
         <v>93.40000000000001</v>
@@ -6705,45 +6705,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M66">
-        <v>54.600192</v>
+        <v>58.81122</v>
       </c>
       <c r="N66">
-        <v>165.0564746666667</v>
+        <v>160.8454466666667</v>
       </c>
       <c r="O66">
-        <v>49.51694240000001</v>
+        <v>48.25363400000001</v>
       </c>
       <c r="P66">
-        <v>115.5395322666667</v>
+        <v>112.5918126666667</v>
       </c>
       <c r="Q66">
-        <v>119.5495322666667</v>
+        <v>116.6018126666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1821712531252706</v>
+        <v>0.1855467791927278</v>
       </c>
       <c r="T66">
-        <v>1.984367896290923</v>
+        <v>2.033485913525846</v>
       </c>
       <c r="U66">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.023001726196616</v>
+        <v>3.734944907904762</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09283287271745473</v>
+        <v>0.09262169430981204</v>
       </c>
       <c r="C67">
-        <v>682.4215620405215</v>
+        <v>671.439362144095</v>
       </c>
       <c r="D67">
-        <v>1548.421562040521</v>
+        <v>1552.199362144095</v>
       </c>
       <c r="E67">
-        <v>623</v>
+        <v>637.7600000000001</v>
       </c>
       <c r="F67">
-        <v>959.4</v>
+        <v>974.1600000000001</v>
       </c>
       <c r="G67">
         <v>93.40000000000001</v>
@@ -6787,28 +6787,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M67">
-        <v>58.81122</v>
+        <v>59.716008</v>
       </c>
       <c r="N67">
-        <v>160.8454466666667</v>
+        <v>159.9406586666667</v>
       </c>
       <c r="O67">
-        <v>48.25363400000001</v>
+        <v>47.98219760000001</v>
       </c>
       <c r="P67">
-        <v>112.5918126666667</v>
+        <v>111.9584610666667</v>
       </c>
       <c r="Q67">
-        <v>116.6018126666667</v>
+        <v>115.9684610666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1855467791927278</v>
+        <v>0.1891208656170943</v>
       </c>
       <c r="T67">
-        <v>2.033485913525846</v>
+        <v>2.085493225892237</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.734944907904762</v>
+        <v>3.678354833542569</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09262169430981204</v>
+        <v>0.09241051590216937</v>
       </c>
       <c r="C68">
-        <v>671.439362144095</v>
+        <v>660.4756412963318</v>
       </c>
       <c r="D68">
-        <v>1552.199362144095</v>
+        <v>1555.995641296332</v>
       </c>
       <c r="E68">
-        <v>637.7600000000001</v>
+        <v>652.5200000000001</v>
       </c>
       <c r="F68">
-        <v>974.1600000000001</v>
+        <v>988.9200000000001</v>
       </c>
       <c r="G68">
         <v>93.40000000000001</v>
@@ -6869,28 +6869,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M68">
-        <v>59.716008</v>
+        <v>60.62079600000001</v>
       </c>
       <c r="N68">
-        <v>159.9406586666667</v>
+        <v>159.0358706666667</v>
       </c>
       <c r="O68">
-        <v>47.98219760000001</v>
+        <v>47.7107612</v>
       </c>
       <c r="P68">
-        <v>111.9584610666667</v>
+        <v>111.3251094666667</v>
       </c>
       <c r="Q68">
-        <v>115.9684610666667</v>
+        <v>115.3351094666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1891208656170943</v>
+        <v>0.1929115633399072</v>
       </c>
       <c r="T68">
-        <v>2.085493225892237</v>
+        <v>2.140652496583862</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.678354833542569</v>
+        <v>3.623454015131485</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09241051590216937</v>
+        <v>0.09219933749452668</v>
       </c>
       <c r="C69">
-        <v>660.4756412963318</v>
+        <v>649.5305354146071</v>
       </c>
       <c r="D69">
-        <v>1555.995641296332</v>
+        <v>1559.810535414607</v>
       </c>
       <c r="E69">
-        <v>652.5200000000001</v>
+        <v>667.2800000000001</v>
       </c>
       <c r="F69">
-        <v>988.9200000000001</v>
+        <v>1003.68</v>
       </c>
       <c r="G69">
         <v>93.40000000000001</v>
@@ -6951,28 +6951,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M69">
-        <v>60.62079600000001</v>
+        <v>61.525584</v>
       </c>
       <c r="N69">
-        <v>159.0358706666667</v>
+        <v>158.1310826666667</v>
       </c>
       <c r="O69">
-        <v>47.7107612</v>
+        <v>47.4393248</v>
       </c>
       <c r="P69">
-        <v>111.3251094666667</v>
+        <v>110.6917578666667</v>
       </c>
       <c r="Q69">
-        <v>115.3351094666667</v>
+        <v>114.7017578666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1929115633399072</v>
+        <v>0.1969391796703959</v>
       </c>
       <c r="T69">
-        <v>2.140652496583862</v>
+        <v>2.199259221693715</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.623454015131485</v>
+        <v>3.570167926673669</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09219933749452668</v>
+        <v>0.09198815908688399</v>
       </c>
       <c r="C70">
-        <v>649.5305354146071</v>
+        <v>638.604181752507</v>
       </c>
       <c r="D70">
-        <v>1559.810535414607</v>
+        <v>1563.644181752507</v>
       </c>
       <c r="E70">
-        <v>667.2800000000001</v>
+        <v>682.0400000000001</v>
       </c>
       <c r="F70">
-        <v>1003.68</v>
+        <v>1018.44</v>
       </c>
       <c r="G70">
         <v>93.40000000000001</v>
@@ -7033,28 +7033,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M70">
-        <v>61.525584</v>
+        <v>62.43037200000001</v>
       </c>
       <c r="N70">
-        <v>158.1310826666667</v>
+        <v>157.2262946666667</v>
       </c>
       <c r="O70">
-        <v>47.4393248</v>
+        <v>47.1678884</v>
       </c>
       <c r="P70">
-        <v>110.6917578666667</v>
+        <v>110.0584062666667</v>
       </c>
       <c r="Q70">
-        <v>114.7017578666667</v>
+        <v>114.0684062666667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1969391796703959</v>
+        <v>0.2012266422157548</v>
       </c>
       <c r="T70">
-        <v>2.199259221693715</v>
+        <v>2.261647025842913</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.570167926673669</v>
+        <v>3.518426362518978</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09198815908688399</v>
+        <v>0.09314898067924129</v>
       </c>
       <c r="C71">
-        <v>638.604181752507</v>
+        <v>603.0009024760943</v>
       </c>
       <c r="D71">
-        <v>1563.644181752507</v>
+        <v>1542.800902476094</v>
       </c>
       <c r="E71">
-        <v>682.0400000000001</v>
+        <v>696.8000000000001</v>
       </c>
       <c r="F71">
-        <v>1018.44</v>
+        <v>1033.2</v>
       </c>
       <c r="G71">
         <v>93.40000000000001</v>
@@ -7115,45 +7115,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M71">
-        <v>62.43037200000001</v>
+        <v>66.22812</v>
       </c>
       <c r="N71">
-        <v>157.2262946666667</v>
+        <v>153.4285466666667</v>
       </c>
       <c r="O71">
-        <v>47.1678884</v>
+        <v>46.02856400000001</v>
       </c>
       <c r="P71">
-        <v>110.0584062666667</v>
+        <v>107.3999826666667</v>
       </c>
       <c r="Q71">
-        <v>114.0684062666667</v>
+        <v>111.4099826666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2012266422157548</v>
+        <v>0.205799935597471</v>
       </c>
       <c r="T71">
-        <v>2.261647025842913</v>
+        <v>2.32819401693539</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.518426362518978</v>
+        <v>3.316667703487079</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09314898067924129</v>
+        <v>0.0929574022715986</v>
       </c>
       <c r="C72">
-        <v>603.0009024760943</v>
+        <v>591.6424422282912</v>
       </c>
       <c r="D72">
-        <v>1542.800902476094</v>
+        <v>1546.202442228291</v>
       </c>
       <c r="E72">
-        <v>696.8000000000001</v>
+        <v>711.5600000000001</v>
       </c>
       <c r="F72">
-        <v>1033.2</v>
+        <v>1047.96</v>
       </c>
       <c r="G72">
         <v>93.40000000000001</v>
@@ -7197,28 +7197,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M72">
-        <v>66.22812</v>
+        <v>67.17423600000001</v>
       </c>
       <c r="N72">
-        <v>153.4285466666667</v>
+        <v>152.4824306666667</v>
       </c>
       <c r="O72">
-        <v>46.02856400000001</v>
+        <v>45.7447292</v>
       </c>
       <c r="P72">
-        <v>107.3999826666667</v>
+        <v>106.7377014666667</v>
       </c>
       <c r="Q72">
-        <v>111.4099826666667</v>
+        <v>110.7477014666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.205799935597471</v>
+        <v>0.2106886285227539</v>
       </c>
       <c r="T72">
-        <v>2.32819401693539</v>
+        <v>2.399330455689418</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.316667703487079</v>
+        <v>3.2699540738605</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0929574022715986</v>
+        <v>0.09276582386395593</v>
       </c>
       <c r="C73">
-        <v>591.6424422282912</v>
+        <v>580.299014431411</v>
       </c>
       <c r="D73">
-        <v>1546.202442228291</v>
+        <v>1549.619014431411</v>
       </c>
       <c r="E73">
-        <v>711.5600000000001</v>
+        <v>726.3200000000001</v>
       </c>
       <c r="F73">
-        <v>1047.96</v>
+        <v>1062.72</v>
       </c>
       <c r="G73">
         <v>93.40000000000001</v>
@@ -7279,28 +7279,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M73">
-        <v>67.17423600000001</v>
+        <v>68.12035200000001</v>
       </c>
       <c r="N73">
-        <v>152.4824306666667</v>
+        <v>151.5363146666667</v>
       </c>
       <c r="O73">
-        <v>45.7447292</v>
+        <v>45.4608944</v>
       </c>
       <c r="P73">
-        <v>106.7377014666667</v>
+        <v>106.0754202666667</v>
       </c>
       <c r="Q73">
-        <v>110.7477014666667</v>
+        <v>110.0854202666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2106886285227538</v>
+        <v>0.2159265137998426</v>
       </c>
       <c r="T73">
-        <v>2.399330455689417</v>
+        <v>2.475548068640161</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.2699540738605</v>
+        <v>3.224538045056882</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09276582386395593</v>
+        <v>0.09257424545631324</v>
       </c>
       <c r="C74">
-        <v>580.299014431411</v>
+        <v>568.970718955673</v>
       </c>
       <c r="D74">
-        <v>1549.619014431411</v>
+        <v>1553.050718955673</v>
       </c>
       <c r="E74">
-        <v>726.3200000000001</v>
+        <v>741.08</v>
       </c>
       <c r="F74">
-        <v>1062.72</v>
+        <v>1077.48</v>
       </c>
       <c r="G74">
         <v>93.40000000000001</v>
@@ -7361,28 +7361,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M74">
-        <v>68.12035200000001</v>
+        <v>69.066468</v>
       </c>
       <c r="N74">
-        <v>151.5363146666667</v>
+        <v>150.5901986666667</v>
       </c>
       <c r="O74">
-        <v>45.4608944</v>
+        <v>45.17705960000001</v>
       </c>
       <c r="P74">
-        <v>106.0754202666667</v>
+        <v>105.4131390666667</v>
       </c>
       <c r="Q74">
-        <v>110.0854202666667</v>
+        <v>109.4231390666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2159265137998426</v>
+        <v>0.2215523905789379</v>
       </c>
       <c r="T74">
-        <v>2.475548068640161</v>
+        <v>2.557411430698367</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.224538045056882</v>
+        <v>3.180366291015007</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09257424545631324</v>
+        <v>0.09238266704867054</v>
       </c>
       <c r="C75">
-        <v>568.970718955673</v>
+        <v>557.6576565579278</v>
       </c>
       <c r="D75">
-        <v>1553.050718955673</v>
+        <v>1556.497656557928</v>
       </c>
       <c r="E75">
-        <v>741.08</v>
+        <v>755.84</v>
       </c>
       <c r="F75">
-        <v>1077.48</v>
+        <v>1092.24</v>
       </c>
       <c r="G75">
         <v>93.40000000000001</v>
@@ -7443,28 +7443,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M75">
-        <v>69.066468</v>
+        <v>70.012584</v>
       </c>
       <c r="N75">
-        <v>150.5901986666667</v>
+        <v>149.6440826666667</v>
       </c>
       <c r="O75">
-        <v>45.17705960000001</v>
+        <v>44.89322480000001</v>
       </c>
       <c r="P75">
-        <v>105.4131390666667</v>
+        <v>104.7508578666667</v>
       </c>
       <c r="Q75">
-        <v>109.4231390666667</v>
+        <v>108.7608578666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2215523905789379</v>
+        <v>0.2276110271102713</v>
       </c>
       <c r="T75">
-        <v>2.557411430698367</v>
+        <v>2.645571974453358</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.180366291015007</v>
+        <v>3.137388368163453</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09238266704867054</v>
+        <v>0.09219108864102785</v>
       </c>
       <c r="C76">
-        <v>557.6576565579278</v>
+        <v>546.3599288915213</v>
       </c>
       <c r="D76">
-        <v>1556.497656557928</v>
+        <v>1559.959928891521</v>
       </c>
       <c r="E76">
-        <v>755.84</v>
+        <v>770.6</v>
       </c>
       <c r="F76">
-        <v>1092.24</v>
+        <v>1107</v>
       </c>
       <c r="G76">
         <v>93.40000000000001</v>
@@ -7525,28 +7525,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M76">
-        <v>70.012584</v>
+        <v>70.95870000000001</v>
       </c>
       <c r="N76">
-        <v>149.6440826666667</v>
+        <v>148.6979666666667</v>
       </c>
       <c r="O76">
-        <v>44.89322480000001</v>
+        <v>44.60939</v>
       </c>
       <c r="P76">
-        <v>104.7508578666667</v>
+        <v>104.0885766666667</v>
       </c>
       <c r="Q76">
-        <v>108.7608578666667</v>
+        <v>108.0985766666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2276110271102713</v>
+        <v>0.2341543545641114</v>
       </c>
       <c r="T76">
-        <v>2.645571974453358</v>
+        <v>2.740785361708749</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.137388368163453</v>
+        <v>3.095556523254607</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09219108864102785</v>
+        <v>0.09199951023338515</v>
       </c>
       <c r="C77">
-        <v>546.3599288915213</v>
+        <v>535.0776385162847</v>
       </c>
       <c r="D77">
-        <v>1559.959928891521</v>
+        <v>1563.437638516285</v>
       </c>
       <c r="E77">
-        <v>770.6</v>
+        <v>785.36</v>
       </c>
       <c r="F77">
-        <v>1107</v>
+        <v>1121.76</v>
       </c>
       <c r="G77">
         <v>93.40000000000001</v>
@@ -7607,28 +7607,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M77">
-        <v>70.95870000000001</v>
+        <v>71.90481600000001</v>
       </c>
       <c r="N77">
-        <v>148.6979666666667</v>
+        <v>147.7518506666667</v>
       </c>
       <c r="O77">
-        <v>44.60939</v>
+        <v>44.3255552</v>
       </c>
       <c r="P77">
-        <v>104.0885766666667</v>
+        <v>103.4262954666667</v>
       </c>
       <c r="Q77">
-        <v>108.0985766666667</v>
+        <v>107.4362954666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2341543545641114</v>
+        <v>0.2412429593057715</v>
       </c>
       <c r="T77">
-        <v>2.740785361708749</v>
+        <v>2.84393319790209</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.095556523254607</v>
+        <v>3.054825516369678</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09199951023338515</v>
+        <v>0.09180793182574247</v>
       </c>
       <c r="C78">
-        <v>535.0776385162847</v>
+        <v>523.8108889086641</v>
       </c>
       <c r="D78">
-        <v>1563.437638516285</v>
+        <v>1566.930888908664</v>
       </c>
       <c r="E78">
-        <v>785.36</v>
+        <v>800.12</v>
       </c>
       <c r="F78">
-        <v>1121.76</v>
+        <v>1136.52</v>
       </c>
       <c r="G78">
         <v>93.40000000000001</v>
@@ -7689,28 +7689,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M78">
-        <v>71.90481600000001</v>
+        <v>72.850932</v>
       </c>
       <c r="N78">
-        <v>147.7518506666667</v>
+        <v>146.8057346666667</v>
       </c>
       <c r="O78">
-        <v>44.3255552</v>
+        <v>44.04172040000001</v>
       </c>
       <c r="P78">
-        <v>103.4262954666667</v>
+        <v>102.7640142666667</v>
       </c>
       <c r="Q78">
-        <v>107.4362954666667</v>
+        <v>106.7740142666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2412429593057715</v>
+        <v>0.2489479644597499</v>
       </c>
       <c r="T78">
-        <v>2.84393319790209</v>
+        <v>2.95605041115572</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.054825516369678</v>
+        <v>3.015152457715526</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09180793182574247</v>
+        <v>0.09587515341809978</v>
       </c>
       <c r="C79">
-        <v>523.8108889086641</v>
+        <v>438.0893345333957</v>
       </c>
       <c r="D79">
-        <v>1566.930888908664</v>
+        <v>1495.969334533396</v>
       </c>
       <c r="E79">
-        <v>800.12</v>
+        <v>814.88</v>
       </c>
       <c r="F79">
-        <v>1136.52</v>
+        <v>1151.28</v>
       </c>
       <c r="G79">
         <v>93.40000000000001</v>
@@ -7771,45 +7771,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M79">
-        <v>72.850932</v>
+        <v>82.77703200000001</v>
       </c>
       <c r="N79">
-        <v>146.8057346666667</v>
+        <v>136.8796346666667</v>
       </c>
       <c r="O79">
-        <v>44.04172040000001</v>
+        <v>41.0638904</v>
       </c>
       <c r="P79">
-        <v>102.7640142666667</v>
+        <v>95.81574426666668</v>
       </c>
       <c r="Q79">
-        <v>106.7740142666667</v>
+        <v>99.82574426666669</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2489479644597499</v>
+        <v>0.2573534246277263</v>
       </c>
       <c r="T79">
-        <v>2.95605041115572</v>
+        <v>3.078360098341499</v>
       </c>
       <c r="U79">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.3</v>
       </c>
       <c r="W79">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.015152457715526</v>
+        <v>2.653594377081153</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09587515341809978</v>
+        <v>0.09573817501045709</v>
       </c>
       <c r="C80">
-        <v>438.0893345333957</v>
+        <v>425.6144762606482</v>
       </c>
       <c r="D80">
-        <v>1495.969334533396</v>
+        <v>1498.254476260648</v>
       </c>
       <c r="E80">
-        <v>814.88</v>
+        <v>829.64</v>
       </c>
       <c r="F80">
-        <v>1151.28</v>
+        <v>1166.04</v>
       </c>
       <c r="G80">
         <v>93.40000000000001</v>
@@ -7853,28 +7853,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M80">
-        <v>82.77703200000001</v>
+        <v>83.83827600000001</v>
       </c>
       <c r="N80">
-        <v>136.8796346666667</v>
+        <v>135.8183906666667</v>
       </c>
       <c r="O80">
-        <v>41.0638904</v>
+        <v>40.7455172</v>
       </c>
       <c r="P80">
-        <v>95.81574426666668</v>
+        <v>95.07287346666669</v>
       </c>
       <c r="Q80">
-        <v>99.82574426666669</v>
+        <v>99.0828734666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2573534246277263</v>
+        <v>0.2665594048117005</v>
       </c>
       <c r="T80">
-        <v>3.078360098341499</v>
+        <v>3.212318327164019</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.653594377081153</v>
+        <v>2.620004574839619</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09573817501045709</v>
+        <v>0.0956011966028144</v>
       </c>
       <c r="C81">
-        <v>425.6144762606482</v>
+        <v>413.1466099246684</v>
       </c>
       <c r="D81">
-        <v>1498.254476260648</v>
+        <v>1500.546609924668</v>
       </c>
       <c r="E81">
-        <v>829.64</v>
+        <v>844.4</v>
       </c>
       <c r="F81">
-        <v>1166.04</v>
+        <v>1180.8</v>
       </c>
       <c r="G81">
         <v>93.40000000000001</v>
@@ -7935,28 +7935,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M81">
-        <v>83.83827600000001</v>
+        <v>84.89952000000001</v>
       </c>
       <c r="N81">
-        <v>135.8183906666667</v>
+        <v>134.7571466666667</v>
       </c>
       <c r="O81">
-        <v>40.7455172</v>
+        <v>40.42714400000001</v>
       </c>
       <c r="P81">
-        <v>95.07287346666669</v>
+        <v>94.3300026666667</v>
       </c>
       <c r="Q81">
-        <v>99.0828734666667</v>
+        <v>98.34000266666671</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2665594048117005</v>
+        <v>0.276685983014072</v>
       </c>
       <c r="T81">
-        <v>3.212318327164019</v>
+        <v>3.35967237886879</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.620004574839619</v>
+        <v>2.587254517654125</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0956011966028144</v>
+        <v>0.0954642181951717</v>
       </c>
       <c r="C82">
-        <v>413.1466099246684</v>
+        <v>400.6857676648754</v>
       </c>
       <c r="D82">
-        <v>1500.546609924668</v>
+        <v>1502.845767664875</v>
       </c>
       <c r="E82">
-        <v>844.4</v>
+        <v>859.1600000000002</v>
       </c>
       <c r="F82">
-        <v>1180.8</v>
+        <v>1195.56</v>
       </c>
       <c r="G82">
         <v>93.40000000000001</v>
@@ -8017,28 +8017,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M82">
-        <v>84.89952000000001</v>
+        <v>85.96076400000003</v>
       </c>
       <c r="N82">
-        <v>134.7571466666667</v>
+        <v>133.6959026666667</v>
       </c>
       <c r="O82">
-        <v>40.42714400000001</v>
+        <v>40.10877079999999</v>
       </c>
       <c r="P82">
-        <v>94.3300026666667</v>
+        <v>93.58713186666665</v>
       </c>
       <c r="Q82">
-        <v>98.34000266666671</v>
+        <v>97.59713186666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.276685983014072</v>
+        <v>0.2878785168166933</v>
       </c>
       <c r="T82">
-        <v>3.35967237886879</v>
+        <v>3.522537383384591</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.587254517654125</v>
+        <v>2.555313103855925</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0954642181951717</v>
+        <v>0.09532723978752902</v>
       </c>
       <c r="C83">
-        <v>400.6857676648754</v>
+        <v>388.231981817969</v>
       </c>
       <c r="D83">
-        <v>1502.845767664875</v>
+        <v>1505.151981817969</v>
       </c>
       <c r="E83">
-        <v>859.1600000000002</v>
+        <v>873.9200000000002</v>
       </c>
       <c r="F83">
-        <v>1195.56</v>
+        <v>1210.32</v>
       </c>
       <c r="G83">
         <v>93.40000000000001</v>
@@ -8099,28 +8099,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M83">
-        <v>85.96076400000003</v>
+        <v>87.02200800000001</v>
       </c>
       <c r="N83">
-        <v>133.6959026666667</v>
+        <v>132.6346586666667</v>
       </c>
       <c r="O83">
-        <v>40.10877079999999</v>
+        <v>39.7903976</v>
       </c>
       <c r="P83">
-        <v>93.58713186666665</v>
+        <v>92.84426106666666</v>
       </c>
       <c r="Q83">
-        <v>97.59713186666666</v>
+        <v>96.85426106666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2878785168166933</v>
+        <v>0.3003146654862724</v>
       </c>
       <c r="T83">
-        <v>3.522537383384591</v>
+        <v>3.703498499513258</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.555313103855925</v>
+        <v>2.524150748930853</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09532723978752902</v>
+        <v>0.09745616137988634</v>
       </c>
       <c r="C84">
-        <v>388.231981817969</v>
+        <v>338.4099813007545</v>
       </c>
       <c r="D84">
-        <v>1505.151981817969</v>
+        <v>1470.089981300755</v>
       </c>
       <c r="E84">
-        <v>873.9200000000002</v>
+        <v>888.6800000000002</v>
       </c>
       <c r="F84">
-        <v>1210.32</v>
+        <v>1225.08</v>
       </c>
       <c r="G84">
         <v>93.40000000000001</v>
@@ -8181,45 +8181,45 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M84">
-        <v>87.02200800000001</v>
+        <v>92.86106400000001</v>
       </c>
       <c r="N84">
-        <v>132.6346586666667</v>
+        <v>126.7956026666667</v>
       </c>
       <c r="O84">
-        <v>39.7903976</v>
+        <v>38.0386808</v>
       </c>
       <c r="P84">
-        <v>92.84426106666666</v>
+        <v>88.75692186666669</v>
       </c>
       <c r="Q84">
-        <v>96.85426106666667</v>
+        <v>92.76692186666669</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3003146654862724</v>
+        <v>0.3142138904699198</v>
       </c>
       <c r="T84">
-        <v>3.703498499513258</v>
+        <v>3.905749158715885</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.3</v>
       </c>
       <c r="W84">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.524150748930853</v>
+        <v>2.365433446537579</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09745616137988634</v>
+        <v>0.09734648297224366</v>
       </c>
       <c r="C85">
-        <v>338.4099813007545</v>
+        <v>325.4163576248056</v>
       </c>
       <c r="D85">
-        <v>1470.089981300755</v>
+        <v>1471.856357624806</v>
       </c>
       <c r="E85">
-        <v>888.6800000000002</v>
+        <v>903.4400000000002</v>
       </c>
       <c r="F85">
-        <v>1225.08</v>
+        <v>1239.84</v>
       </c>
       <c r="G85">
         <v>93.40000000000001</v>
@@ -8263,28 +8263,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M85">
-        <v>92.86106400000001</v>
+        <v>93.97987200000001</v>
       </c>
       <c r="N85">
-        <v>126.7956026666667</v>
+        <v>125.6767946666667</v>
       </c>
       <c r="O85">
-        <v>38.0386808</v>
+        <v>37.7030384</v>
       </c>
       <c r="P85">
-        <v>88.75692186666669</v>
+        <v>87.97375626666667</v>
       </c>
       <c r="Q85">
-        <v>92.76692186666669</v>
+        <v>91.98375626666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3142138904699198</v>
+        <v>0.329850518576523</v>
       </c>
       <c r="T85">
-        <v>3.905749158715885</v>
+        <v>4.133281150318842</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.365433446537579</v>
+        <v>2.337273524554988</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09734648297224366</v>
+        <v>0.09723680456460097</v>
       </c>
       <c r="C86">
-        <v>325.4163576248059</v>
+        <v>312.4269838094567</v>
       </c>
       <c r="D86">
-        <v>1471.856357624806</v>
+        <v>1473.626983809457</v>
       </c>
       <c r="E86">
-        <v>903.4399999999999</v>
+        <v>918.1999999999999</v>
       </c>
       <c r="F86">
-        <v>1239.84</v>
+        <v>1254.6</v>
       </c>
       <c r="G86">
         <v>93.40000000000001</v>
@@ -8345,28 +8345,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M86">
-        <v>93.979872</v>
+        <v>95.09868</v>
       </c>
       <c r="N86">
-        <v>125.6767946666667</v>
+        <v>124.5579866666667</v>
       </c>
       <c r="O86">
-        <v>37.7030384</v>
+        <v>37.36739600000001</v>
       </c>
       <c r="P86">
-        <v>87.9737562666667</v>
+        <v>87.19059066666668</v>
       </c>
       <c r="Q86">
-        <v>91.9837562666667</v>
+        <v>91.20059066666668</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3298505185765228</v>
+        <v>0.3475720304306731</v>
       </c>
       <c r="T86">
-        <v>4.133281150318839</v>
+        <v>4.39115074080219</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.337273524554988</v>
+        <v>2.309776188971989</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09723680456460097</v>
+        <v>0.09712712615695827</v>
       </c>
       <c r="C87">
-        <v>312.4269838094567</v>
+        <v>299.4418752107802</v>
       </c>
       <c r="D87">
-        <v>1473.626983809457</v>
+        <v>1475.40187521078</v>
       </c>
       <c r="E87">
-        <v>918.1999999999999</v>
+        <v>932.9599999999999</v>
       </c>
       <c r="F87">
-        <v>1254.6</v>
+        <v>1269.36</v>
       </c>
       <c r="G87">
         <v>93.40000000000001</v>
@@ -8427,28 +8427,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M87">
-        <v>95.09868</v>
+        <v>96.217488</v>
       </c>
       <c r="N87">
-        <v>124.5579866666667</v>
+        <v>123.4391786666667</v>
       </c>
       <c r="O87">
-        <v>37.36739600000001</v>
+        <v>37.03175360000001</v>
       </c>
       <c r="P87">
-        <v>87.19059066666668</v>
+        <v>86.40742506666669</v>
       </c>
       <c r="Q87">
-        <v>91.20059066666668</v>
+        <v>90.41742506666669</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3475720304306731</v>
+        <v>0.3678251868354162</v>
       </c>
       <c r="T87">
-        <v>4.39115074080219</v>
+        <v>4.685858844211732</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.309776188971989</v>
+        <v>2.282918326309524</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09712712615695827</v>
+        <v>0.09701744774931559</v>
       </c>
       <c r="C88">
-        <v>299.4418752107802</v>
+        <v>286.4610472589193</v>
       </c>
       <c r="D88">
-        <v>1475.40187521078</v>
+        <v>1477.181047258919</v>
       </c>
       <c r="E88">
-        <v>932.9599999999999</v>
+        <v>947.7199999999999</v>
       </c>
       <c r="F88">
-        <v>1269.36</v>
+        <v>1284.12</v>
       </c>
       <c r="G88">
         <v>93.40000000000001</v>
@@ -8509,28 +8509,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M88">
-        <v>96.217488</v>
+        <v>97.336296</v>
       </c>
       <c r="N88">
-        <v>123.4391786666667</v>
+        <v>122.3203706666667</v>
       </c>
       <c r="O88">
-        <v>37.03175360000001</v>
+        <v>36.6961112</v>
       </c>
       <c r="P88">
-        <v>86.40742506666669</v>
+        <v>85.62425946666669</v>
       </c>
       <c r="Q88">
-        <v>90.41742506666669</v>
+        <v>89.63425946666669</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3678251868354162</v>
+        <v>0.3911942134562738</v>
       </c>
       <c r="T88">
-        <v>4.685858844211732</v>
+        <v>5.025906655838129</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.282918326309524</v>
+        <v>2.25667788577723</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09701744774931559</v>
+        <v>0.0969077693416729</v>
       </c>
       <c r="C89">
-        <v>286.4610472589193</v>
+        <v>273.484515458536</v>
       </c>
       <c r="D89">
-        <v>1477.181047258919</v>
+        <v>1478.964515458536</v>
       </c>
       <c r="E89">
-        <v>947.7199999999999</v>
+        <v>962.4800000000001</v>
       </c>
       <c r="F89">
-        <v>1284.12</v>
+        <v>1298.88</v>
       </c>
       <c r="G89">
         <v>93.40000000000001</v>
@@ -8591,28 +8591,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M89">
-        <v>97.336296</v>
+        <v>98.45510400000002</v>
       </c>
       <c r="N89">
-        <v>122.3203706666667</v>
+        <v>121.2015626666667</v>
       </c>
       <c r="O89">
-        <v>36.6961112</v>
+        <v>36.3604688</v>
       </c>
       <c r="P89">
-        <v>85.62425946666669</v>
+        <v>84.84109386666668</v>
       </c>
       <c r="Q89">
-        <v>89.63425946666669</v>
+        <v>88.85109386666669</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3911942134562738</v>
+        <v>0.4184580778472742</v>
       </c>
       <c r="T89">
-        <v>5.025906655838129</v>
+        <v>5.422629102735591</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.25667788577723</v>
+        <v>2.231033818893398</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0969077693416729</v>
+        <v>0.09679809093403022</v>
       </c>
       <c r="C90">
-        <v>273.484515458536</v>
+        <v>260.5122953892608</v>
       </c>
       <c r="D90">
-        <v>1478.964515458536</v>
+        <v>1480.752295389261</v>
       </c>
       <c r="E90">
-        <v>962.4800000000001</v>
+        <v>977.2400000000001</v>
       </c>
       <c r="F90">
-        <v>1298.88</v>
+        <v>1313.64</v>
       </c>
       <c r="G90">
         <v>93.40000000000001</v>
@@ -8673,28 +8673,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M90">
-        <v>98.45510400000002</v>
+        <v>99.57391200000002</v>
       </c>
       <c r="N90">
-        <v>121.2015626666667</v>
+        <v>120.0827546666667</v>
       </c>
       <c r="O90">
-        <v>36.3604688</v>
+        <v>36.0248264</v>
       </c>
       <c r="P90">
-        <v>84.84109386666668</v>
+        <v>84.05792826666666</v>
       </c>
       <c r="Q90">
-        <v>88.85109386666669</v>
+        <v>88.06792826666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4184580778472742</v>
+        <v>0.4506790084911838</v>
       </c>
       <c r="T90">
-        <v>5.422629102735591</v>
+        <v>5.891482903614409</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.231033818893398</v>
+        <v>2.205966023175495</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09679809093403022</v>
+        <v>0.09668841252638752</v>
       </c>
       <c r="C91">
-        <v>260.5122953892608</v>
+        <v>247.544402706146</v>
       </c>
       <c r="D91">
-        <v>1480.752295389261</v>
+        <v>1482.544402706146</v>
       </c>
       <c r="E91">
-        <v>977.2400000000001</v>
+        <v>992.0000000000001</v>
       </c>
       <c r="F91">
-        <v>1313.64</v>
+        <v>1328.4</v>
       </c>
       <c r="G91">
         <v>93.40000000000001</v>
@@ -8755,28 +8755,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M91">
-        <v>99.57391200000002</v>
+        <v>100.69272</v>
       </c>
       <c r="N91">
-        <v>120.0827546666667</v>
+        <v>118.9639466666667</v>
       </c>
       <c r="O91">
-        <v>36.0248264</v>
+        <v>35.689184</v>
       </c>
       <c r="P91">
-        <v>84.05792826666666</v>
+        <v>83.27476266666667</v>
       </c>
       <c r="Q91">
-        <v>88.06792826666667</v>
+        <v>87.28476266666668</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4506790084911838</v>
+        <v>0.4893441252638753</v>
       </c>
       <c r="T91">
-        <v>5.891482903614409</v>
+        <v>6.454107464668992</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.205966023175495</v>
+        <v>2.181455289584656</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09668841252638752</v>
+        <v>0.09657873411874483</v>
       </c>
       <c r="C92">
-        <v>247.544402706146</v>
+        <v>234.5808531401226</v>
       </c>
       <c r="D92">
-        <v>1482.544402706146</v>
+        <v>1484.340853140123</v>
       </c>
       <c r="E92">
-        <v>992.0000000000001</v>
+        <v>1006.76</v>
       </c>
       <c r="F92">
-        <v>1328.4</v>
+        <v>1343.16</v>
       </c>
       <c r="G92">
         <v>93.40000000000001</v>
@@ -8837,28 +8837,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M92">
-        <v>100.69272</v>
+        <v>101.811528</v>
       </c>
       <c r="N92">
-        <v>118.9639466666667</v>
+        <v>117.8451386666667</v>
       </c>
       <c r="O92">
-        <v>35.689184</v>
+        <v>35.35354160000001</v>
       </c>
       <c r="P92">
-        <v>83.27476266666667</v>
+        <v>82.49159706666669</v>
       </c>
       <c r="Q92">
-        <v>87.28476266666668</v>
+        <v>86.50159706666669</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4893441252638753</v>
+        <v>0.5366014902082761</v>
       </c>
       <c r="T92">
-        <v>6.454107464668992</v>
+        <v>7.141759705957926</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.181455289584656</v>
+        <v>2.157483253435374</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09657873411874483</v>
+        <v>0.09646905571110215</v>
       </c>
       <c r="C93">
-        <v>234.5808531401226</v>
+        <v>221.6216624984611</v>
       </c>
       <c r="D93">
-        <v>1484.340853140123</v>
+        <v>1486.141662498461</v>
       </c>
       <c r="E93">
-        <v>1006.76</v>
+        <v>1021.52</v>
       </c>
       <c r="F93">
-        <v>1343.16</v>
+        <v>1357.92</v>
       </c>
       <c r="G93">
         <v>93.40000000000001</v>
@@ -8919,28 +8919,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M93">
-        <v>101.811528</v>
+        <v>102.930336</v>
       </c>
       <c r="N93">
-        <v>117.8451386666667</v>
+        <v>116.7263306666667</v>
       </c>
       <c r="O93">
-        <v>35.35354160000001</v>
+        <v>35.0178992</v>
       </c>
       <c r="P93">
-        <v>82.49159706666669</v>
+        <v>81.70843146666668</v>
       </c>
       <c r="Q93">
-        <v>86.50159706666669</v>
+        <v>85.71843146666669</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5366014902082761</v>
+        <v>0.595673196388777</v>
       </c>
       <c r="T93">
-        <v>7.141759705957926</v>
+        <v>8.001325007569095</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.157483253435374</v>
+        <v>2.134032348506729</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09646905571110215</v>
+        <v>0.09635937730345945</v>
       </c>
       <c r="C94">
-        <v>221.6216624984611</v>
+        <v>208.6668466652361</v>
       </c>
       <c r="D94">
-        <v>1486.141662498461</v>
+        <v>1487.946846665236</v>
       </c>
       <c r="E94">
-        <v>1021.52</v>
+        <v>1036.28</v>
       </c>
       <c r="F94">
-        <v>1357.92</v>
+        <v>1372.68</v>
       </c>
       <c r="G94">
         <v>93.40000000000001</v>
@@ -9001,28 +9001,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M94">
-        <v>102.930336</v>
+        <v>104.049144</v>
       </c>
       <c r="N94">
-        <v>116.7263306666667</v>
+        <v>115.6075226666667</v>
       </c>
       <c r="O94">
-        <v>35.0178992</v>
+        <v>34.6822568</v>
       </c>
       <c r="P94">
-        <v>81.70843146666668</v>
+        <v>80.92526586666668</v>
       </c>
       <c r="Q94">
-        <v>85.71843146666669</v>
+        <v>84.93526586666668</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.595673196388777</v>
+        <v>0.6716225329065639</v>
       </c>
       <c r="T94">
-        <v>8.001325007569095</v>
+        <v>9.106480395354883</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.134032348506729</v>
+        <v>2.111085764114183</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09635937730345945</v>
+        <v>0.09624969889581678</v>
       </c>
       <c r="C95">
-        <v>208.6668466652361</v>
+        <v>195.71642160179</v>
       </c>
       <c r="D95">
-        <v>1487.946846665236</v>
+        <v>1489.75642160179</v>
       </c>
       <c r="E95">
-        <v>1036.28</v>
+        <v>1051.04</v>
       </c>
       <c r="F95">
-        <v>1372.68</v>
+        <v>1387.44</v>
       </c>
       <c r="G95">
         <v>93.40000000000001</v>
@@ -9083,28 +9083,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M95">
-        <v>104.049144</v>
+        <v>105.167952</v>
       </c>
       <c r="N95">
-        <v>115.6075226666667</v>
+        <v>114.4887146666667</v>
       </c>
       <c r="O95">
-        <v>34.6822568</v>
+        <v>34.3466144</v>
       </c>
       <c r="P95">
-        <v>80.92526586666668</v>
+        <v>80.14210026666669</v>
       </c>
       <c r="Q95">
-        <v>84.93526586666668</v>
+        <v>84.15210026666669</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6716225329065639</v>
+        <v>0.7728883149302801</v>
       </c>
       <c r="T95">
-        <v>9.106480395354883</v>
+        <v>10.5800209124026</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.111085764114183</v>
+        <v>2.088627404921479</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09624969889581678</v>
+        <v>0.09614002048817408</v>
       </c>
       <c r="C96">
-        <v>195.71642160179</v>
+        <v>182.7704033472085</v>
       </c>
       <c r="D96">
-        <v>1489.75642160179</v>
+        <v>1491.570403347208</v>
       </c>
       <c r="E96">
-        <v>1051.04</v>
+        <v>1065.8</v>
       </c>
       <c r="F96">
-        <v>1387.44</v>
+        <v>1402.2</v>
       </c>
       <c r="G96">
         <v>93.40000000000001</v>
@@ -9165,28 +9165,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M96">
-        <v>105.167952</v>
+        <v>106.28676</v>
       </c>
       <c r="N96">
-        <v>114.4887146666667</v>
+        <v>113.3699066666667</v>
       </c>
       <c r="O96">
-        <v>34.3466144</v>
+        <v>34.010972</v>
       </c>
       <c r="P96">
-        <v>80.14210026666669</v>
+        <v>79.35893466666667</v>
       </c>
       <c r="Q96">
-        <v>84.15210026666669</v>
+        <v>83.36893466666668</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7728883149302801</v>
+        <v>0.9146604097634827</v>
       </c>
       <c r="T96">
-        <v>10.5800209124026</v>
+        <v>12.64297763626941</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.088627404921479</v>
+        <v>2.066641853290727</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09614002048817408</v>
+        <v>0.09603034208053141</v>
       </c>
       <c r="C97">
-        <v>182.7704033472085</v>
+        <v>169.8288080187888</v>
       </c>
       <c r="D97">
-        <v>1491.570403347208</v>
+        <v>1493.388808018789</v>
       </c>
       <c r="E97">
-        <v>1065.8</v>
+        <v>1080.56</v>
       </c>
       <c r="F97">
-        <v>1402.2</v>
+        <v>1416.96</v>
       </c>
       <c r="G97">
         <v>93.40000000000001</v>
@@ -9247,28 +9247,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M97">
-        <v>106.28676</v>
+        <v>107.405568</v>
       </c>
       <c r="N97">
-        <v>113.3699066666667</v>
+        <v>112.2510986666667</v>
       </c>
       <c r="O97">
-        <v>34.010972</v>
+        <v>33.6753296</v>
       </c>
       <c r="P97">
-        <v>79.35893466666667</v>
+        <v>78.57576906666668</v>
       </c>
       <c r="Q97">
-        <v>83.36893466666668</v>
+        <v>82.58576906666669</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9146604097634827</v>
+        <v>1.127318552013287</v>
       </c>
       <c r="T97">
-        <v>12.64297763626941</v>
+        <v>15.73741272206962</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.066641853290727</v>
+        <v>2.045114333985615</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09603034208053139</v>
+        <v>0.09592066367288871</v>
       </c>
       <c r="C98">
-        <v>169.828808018789</v>
+        <v>156.8916518125222</v>
       </c>
       <c r="D98">
-        <v>1493.388808018789</v>
+        <v>1495.211651812522</v>
       </c>
       <c r="E98">
-        <v>1080.56</v>
+        <v>1095.32</v>
       </c>
       <c r="F98">
-        <v>1416.96</v>
+        <v>1431.72</v>
       </c>
       <c r="G98">
         <v>93.40000000000001</v>
@@ -9329,28 +9329,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M98">
-        <v>107.405568</v>
+        <v>108.524376</v>
       </c>
       <c r="N98">
-        <v>112.2510986666667</v>
+        <v>111.1322906666667</v>
       </c>
       <c r="O98">
-        <v>33.6753296</v>
+        <v>33.3396872</v>
       </c>
       <c r="P98">
-        <v>78.57576906666668</v>
+        <v>77.79260346666668</v>
       </c>
       <c r="Q98">
-        <v>82.58576906666669</v>
+        <v>81.80260346666668</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.127318552013284</v>
+        <v>1.481748789096289</v>
       </c>
       <c r="T98">
-        <v>15.73741272206958</v>
+        <v>20.89480453173658</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.045114333985615</v>
+        <v>2.024030681057928</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09592066367288871</v>
+        <v>0.09581098526524602</v>
       </c>
       <c r="C99">
-        <v>156.8916518125222</v>
+        <v>143.958951003571</v>
       </c>
       <c r="D99">
-        <v>1495.211651812522</v>
+        <v>1497.038951003571</v>
       </c>
       <c r="E99">
-        <v>1095.32</v>
+        <v>1110.08</v>
       </c>
       <c r="F99">
-        <v>1431.72</v>
+        <v>1446.48</v>
       </c>
       <c r="G99">
         <v>93.40000000000001</v>
@@ -9411,28 +9411,28 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M99">
-        <v>108.524376</v>
+        <v>109.643184</v>
       </c>
       <c r="N99">
-        <v>111.1322906666667</v>
+        <v>110.0134826666667</v>
       </c>
       <c r="O99">
-        <v>33.3396872</v>
+        <v>33.0040448</v>
       </c>
       <c r="P99">
-        <v>77.79260346666668</v>
+        <v>77.00943786666669</v>
       </c>
       <c r="Q99">
-        <v>81.80260346666668</v>
+        <v>81.01943786666669</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.481748789096289</v>
+        <v>2.190609263262299</v>
       </c>
       <c r="T99">
-        <v>20.89480453173658</v>
+        <v>31.20958815107057</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.024030681057928</v>
+        <v>2.003377306761419</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09581098526524602</v>
+        <v>0.1055419068576033</v>
       </c>
       <c r="C100">
-        <v>143.958951003571</v>
+        <v>-17.24303053155791</v>
       </c>
       <c r="D100">
-        <v>1497.038951003571</v>
+        <v>1350.596969468442</v>
       </c>
       <c r="E100">
-        <v>1110.08</v>
+        <v>1124.84</v>
       </c>
       <c r="F100">
-        <v>1446.48</v>
+        <v>1461.24</v>
       </c>
       <c r="G100">
         <v>93.40000000000001</v>
@@ -9493,129 +9493,47 @@
         <v>219.6566666666667</v>
       </c>
       <c r="M100">
-        <v>109.643184</v>
+        <v>131.5116</v>
       </c>
       <c r="N100">
-        <v>110.0134826666667</v>
+        <v>88.14506666666671</v>
       </c>
       <c r="O100">
-        <v>33.0040448</v>
+        <v>26.44352000000001</v>
       </c>
       <c r="P100">
-        <v>77.00943786666669</v>
+        <v>61.7015466666667</v>
       </c>
       <c r="Q100">
-        <v>81.01943786666669</v>
+        <v>65.71154666666671</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.190609263262299</v>
+        <v>4.317190685760329</v>
       </c>
       <c r="T100">
-        <v>31.20958815107057</v>
+        <v>62.15393900907256</v>
       </c>
       <c r="U100">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V100">
         <v>0.3</v>
       </c>
       <c r="W100">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.003377306761419</v>
+        <v>1.670245565156737</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1055419068576033</v>
-      </c>
-      <c r="C101">
-        <v>-17.24303053155791</v>
-      </c>
-      <c r="D101">
-        <v>1350.596969468442</v>
-      </c>
-      <c r="E101">
-        <v>1124.84</v>
-      </c>
-      <c r="F101">
-        <v>1461.24</v>
-      </c>
-      <c r="G101">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>1139.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>223.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>4.01</v>
-      </c>
-      <c r="L101">
-        <v>219.6566666666667</v>
-      </c>
-      <c r="M101">
-        <v>131.5116</v>
-      </c>
-      <c r="N101">
-        <v>88.14506666666671</v>
-      </c>
-      <c r="O101">
-        <v>26.44352000000001</v>
-      </c>
-      <c r="P101">
-        <v>61.7015466666667</v>
-      </c>
-      <c r="Q101">
-        <v>65.71154666666671</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.317190685760329</v>
-      </c>
-      <c r="T101">
-        <v>62.15393900907256</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.670245565156737</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
